--- a/research/traditional_assets/database/data/netherlands/netherlands_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_electronics_general.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1010791058622659</v>
+        <v>0.1008517117691412</v>
       </c>
       <c r="C2">
-        <v>387.9717338124793</v>
+        <v>385.5934567698874</v>
       </c>
       <c r="D2">
-        <v>386.3217338124794</v>
+        <v>387.9174567698875</v>
       </c>
       <c r="E2">
-        <v>-24.2</v>
+        <v>-20.226</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.974</v>
       </c>
       <c r="G2">
         <v>1.65</v>
@@ -1451,28 +1451,28 @@
         <v>21.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1998922</v>
       </c>
       <c r="N2">
-        <v>21.9</v>
+        <v>21.7001078</v>
       </c>
       <c r="O2">
-        <v>5.6502</v>
+        <v>5.598627812399999</v>
       </c>
       <c r="P2">
-        <v>16.2498</v>
+        <v>16.1014799876</v>
       </c>
       <c r="Q2">
-        <v>27.3498</v>
+        <v>27.2014799876</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1010791058622659</v>
+        <v>0.1014934199688295</v>
       </c>
       <c r="T2">
-        <v>1.276653715063877</v>
+        <v>1.286222170180821</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>109.5590523292055</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1008517117691412</v>
+        <v>0.1006243176760166</v>
       </c>
       <c r="C3">
-        <v>385.5934567698874</v>
+        <v>383.2284168450621</v>
       </c>
       <c r="D3">
-        <v>387.9174567698875</v>
+        <v>389.5264168450621</v>
       </c>
       <c r="E3">
-        <v>-20.226</v>
+        <v>-16.252</v>
       </c>
       <c r="F3">
-        <v>3.974</v>
+        <v>7.948</v>
       </c>
       <c r="G3">
         <v>1.65</v>
@@ -1533,28 +1533,28 @@
         <v>21.9</v>
       </c>
       <c r="M3">
-        <v>0.1998922</v>
+        <v>0.3997843999999999</v>
       </c>
       <c r="N3">
-        <v>21.7001078</v>
+        <v>21.5002156</v>
       </c>
       <c r="O3">
-        <v>5.598627812399999</v>
+        <v>5.5470556248</v>
       </c>
       <c r="P3">
-        <v>16.1014799876</v>
+        <v>15.9531599752</v>
       </c>
       <c r="Q3">
-        <v>27.2014799876</v>
+        <v>27.0531599752</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1014934199688295</v>
+        <v>0.101916189465323</v>
       </c>
       <c r="T3">
-        <v>1.286222170180821</v>
+        <v>1.295985899891987</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>109.5590523292055</v>
+        <v>54.77952616460272</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1006243176760166</v>
+        <v>0.1003969235828919</v>
       </c>
       <c r="C4">
-        <v>383.2284168450621</v>
+        <v>380.8767794342672</v>
       </c>
       <c r="D4">
-        <v>389.5264168450621</v>
+        <v>391.1487794342673</v>
       </c>
       <c r="E4">
-        <v>-16.252</v>
+        <v>-12.278</v>
       </c>
       <c r="F4">
-        <v>7.948</v>
+        <v>11.922</v>
       </c>
       <c r="G4">
         <v>1.65</v>
@@ -1615,28 +1615,28 @@
         <v>21.9</v>
       </c>
       <c r="M4">
-        <v>0.3997843999999999</v>
+        <v>0.5996765999999999</v>
       </c>
       <c r="N4">
-        <v>21.5002156</v>
+        <v>21.3003234</v>
       </c>
       <c r="O4">
-        <v>5.5470556248</v>
+        <v>5.4954834372</v>
       </c>
       <c r="P4">
-        <v>15.9531599752</v>
+        <v>15.8048399628</v>
       </c>
       <c r="Q4">
-        <v>27.0531599752</v>
+        <v>26.9048399628</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.101916189465323</v>
+        <v>0.1023476758586515</v>
       </c>
       <c r="T4">
-        <v>1.295985899891987</v>
+        <v>1.305950943617817</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>54.77952616460272</v>
+        <v>36.51968410973515</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1003969235828919</v>
+        <v>0.1001695294897673</v>
       </c>
       <c r="C5">
-        <v>380.8767794342672</v>
+        <v>378.5387127007673</v>
       </c>
       <c r="D5">
-        <v>391.1487794342673</v>
+        <v>392.7847127007673</v>
       </c>
       <c r="E5">
-        <v>-12.278</v>
+        <v>-8.304</v>
       </c>
       <c r="F5">
-        <v>11.922</v>
+        <v>15.896</v>
       </c>
       <c r="G5">
         <v>1.65</v>
@@ -1697,28 +1697,28 @@
         <v>21.9</v>
       </c>
       <c r="M5">
-        <v>0.5996765999999999</v>
+        <v>0.7995687999999999</v>
       </c>
       <c r="N5">
-        <v>21.3003234</v>
+        <v>21.1004312</v>
       </c>
       <c r="O5">
-        <v>5.4954834372</v>
+        <v>5.4439112496</v>
       </c>
       <c r="P5">
-        <v>15.8048399628</v>
+        <v>15.6565199504</v>
       </c>
       <c r="Q5">
-        <v>26.9048399628</v>
+        <v>26.7565199504</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1023476758586515</v>
+        <v>0.1027881515518409</v>
       </c>
       <c r="T5">
-        <v>1.305950943617817</v>
+        <v>1.316123592421269</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>36.51968410973515</v>
+        <v>27.38976308230136</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1001695294897673</v>
+        <v>0.09994213539664262</v>
       </c>
       <c r="C6">
-        <v>378.5387127007673</v>
+        <v>376.2143876329342</v>
       </c>
       <c r="D6">
-        <v>392.7847127007673</v>
+        <v>394.4343876329342</v>
       </c>
       <c r="E6">
-        <v>-8.304</v>
+        <v>-4.329999999999998</v>
       </c>
       <c r="F6">
-        <v>15.896</v>
+        <v>19.87</v>
       </c>
       <c r="G6">
         <v>1.65</v>
@@ -1779,28 +1779,28 @@
         <v>21.9</v>
       </c>
       <c r="M6">
-        <v>0.7995687999999999</v>
+        <v>0.999461</v>
       </c>
       <c r="N6">
-        <v>21.1004312</v>
+        <v>20.900539</v>
       </c>
       <c r="O6">
-        <v>5.4439112496</v>
+        <v>5.392339062</v>
       </c>
       <c r="P6">
-        <v>15.6565199504</v>
+        <v>15.508199938</v>
       </c>
       <c r="Q6">
-        <v>26.7565199504</v>
+        <v>26.608199938</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1027881515518409</v>
+        <v>0.1032379004175186</v>
       </c>
       <c r="T6">
-        <v>1.316123592421269</v>
+        <v>1.326510402252161</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>27.38976308230136</v>
+        <v>21.91181046584109</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09994213539664262</v>
+        <v>0.09971474130351798</v>
       </c>
       <c r="C7">
-        <v>376.2143876329342</v>
+        <v>373.9039781038229</v>
       </c>
       <c r="D7">
-        <v>394.4343876329342</v>
+        <v>396.0979781038229</v>
       </c>
       <c r="E7">
-        <v>-4.329999999999998</v>
+        <v>-0.3559999999999981</v>
       </c>
       <c r="F7">
-        <v>19.87</v>
+        <v>23.844</v>
       </c>
       <c r="G7">
         <v>1.65</v>
@@ -1861,28 +1861,28 @@
         <v>21.9</v>
       </c>
       <c r="M7">
-        <v>0.999461</v>
+        <v>1.1993532</v>
       </c>
       <c r="N7">
-        <v>20.900539</v>
+        <v>20.7006468</v>
       </c>
       <c r="O7">
-        <v>5.392339062</v>
+        <v>5.3407668744</v>
       </c>
       <c r="P7">
-        <v>15.508199938</v>
+        <v>15.3598799256</v>
       </c>
       <c r="Q7">
-        <v>26.608199938</v>
+        <v>26.4598799256</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1032379004175186</v>
+        <v>0.1036972184079979</v>
       </c>
       <c r="T7">
-        <v>1.326510402252161</v>
+        <v>1.337118208036903</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>21.91181046584109</v>
+        <v>18.25984205486757</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09971474130351798</v>
+        <v>0.09948734721039337</v>
       </c>
       <c r="C8">
-        <v>373.9039781038229</v>
+        <v>371.6076609322636</v>
       </c>
       <c r="D8">
-        <v>396.0979781038229</v>
+        <v>397.7756609322636</v>
       </c>
       <c r="E8">
-        <v>-0.3560000000000016</v>
+        <v>3.617999999999995</v>
       </c>
       <c r="F8">
-        <v>23.844</v>
+        <v>27.81799999999999</v>
       </c>
       <c r="G8">
         <v>1.65</v>
@@ -1943,28 +1943,28 @@
         <v>21.9</v>
       </c>
       <c r="M8">
-        <v>1.1993532</v>
+        <v>1.3992454</v>
       </c>
       <c r="N8">
-        <v>20.7006468</v>
+        <v>20.5007546</v>
       </c>
       <c r="O8">
-        <v>5.3407668744</v>
+        <v>5.2891946868</v>
       </c>
       <c r="P8">
-        <v>15.3598799256</v>
+        <v>15.2115599132</v>
       </c>
       <c r="Q8">
-        <v>26.4598799256</v>
+        <v>26.3115599132</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1036972184079979</v>
+        <v>0.104166414204724</v>
       </c>
       <c r="T8">
-        <v>1.337118208036903</v>
+        <v>1.34795413867723</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.25984205486758</v>
+        <v>15.6512931898865</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09948734721039336</v>
+        <v>0.09925995311726871</v>
       </c>
       <c r="C9">
-        <v>371.6076609322637</v>
+        <v>369.3256159455115</v>
       </c>
       <c r="D9">
-        <v>397.7756609322637</v>
+        <v>399.4676159455115</v>
       </c>
       <c r="E9">
-        <v>3.618000000000002</v>
+        <v>7.591999999999999</v>
       </c>
       <c r="F9">
-        <v>27.818</v>
+        <v>31.792</v>
       </c>
       <c r="G9">
         <v>1.65</v>
@@ -2025,28 +2025,28 @@
         <v>21.9</v>
       </c>
       <c r="M9">
-        <v>1.3992454</v>
+        <v>1.5991376</v>
       </c>
       <c r="N9">
-        <v>20.5007546</v>
+        <v>20.3008624</v>
       </c>
       <c r="O9">
-        <v>5.289194686799999</v>
+        <v>5.2376224992</v>
       </c>
       <c r="P9">
-        <v>15.2115599132</v>
+        <v>15.0632399008</v>
       </c>
       <c r="Q9">
-        <v>26.3115599132</v>
+        <v>26.1632399008</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.104166414204724</v>
+        <v>0.1046458099100747</v>
       </c>
       <c r="T9">
-        <v>1.34795413867723</v>
+        <v>1.359025633027129</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.65129318988649</v>
+        <v>13.69488154115068</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09925995311726871</v>
+        <v>0.09913272902414406</v>
       </c>
       <c r="C10">
-        <v>369.3256159455115</v>
+        <v>366.3045374648345</v>
       </c>
       <c r="D10">
-        <v>399.4676159455115</v>
+        <v>400.4205374648345</v>
       </c>
       <c r="E10">
-        <v>7.591999999999999</v>
+        <v>11.566</v>
       </c>
       <c r="F10">
-        <v>31.792</v>
+        <v>35.766</v>
       </c>
       <c r="G10">
         <v>1.65</v>
@@ -2107,45 +2107,45 @@
         <v>21.9</v>
       </c>
       <c r="M10">
-        <v>1.5991376</v>
+        <v>1.8526788</v>
       </c>
       <c r="N10">
-        <v>20.3008624</v>
+        <v>20.0473212</v>
       </c>
       <c r="O10">
-        <v>5.2376224992</v>
+        <v>5.172208869599999</v>
       </c>
       <c r="P10">
-        <v>15.0632399008</v>
+        <v>14.8751123304</v>
       </c>
       <c r="Q10">
-        <v>26.1632399008</v>
+        <v>25.9751123304</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1046458099100747</v>
+        <v>0.1051357417847737</v>
       </c>
       <c r="T10">
-        <v>1.359025633027129</v>
+        <v>1.37034045692318</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.258</v>
       </c>
       <c r="W10">
-        <v>0.0373226</v>
+        <v>0.0384356</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.69488154115068</v>
+        <v>11.82072143320256</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09913272902414406</v>
+        <v>0.09891646493101941</v>
       </c>
       <c r="C11">
-        <v>366.3045374648345</v>
+        <v>363.9608527449604</v>
       </c>
       <c r="D11">
-        <v>400.4205374648345</v>
+        <v>402.0508527449605</v>
       </c>
       <c r="E11">
-        <v>11.566</v>
+        <v>15.54</v>
       </c>
       <c r="F11">
-        <v>35.766</v>
+        <v>39.73999999999999</v>
       </c>
       <c r="G11">
         <v>1.65</v>
@@ -2189,28 +2189,28 @@
         <v>21.9</v>
       </c>
       <c r="M11">
-        <v>1.8526788</v>
+        <v>2.058532</v>
       </c>
       <c r="N11">
-        <v>20.0473212</v>
+        <v>19.841468</v>
       </c>
       <c r="O11">
-        <v>5.172208869599999</v>
+        <v>5.119098744</v>
       </c>
       <c r="P11">
-        <v>14.8751123304</v>
+        <v>14.722369256</v>
       </c>
       <c r="Q11">
-        <v>25.9751123304</v>
+        <v>25.822369256</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1051357417847737</v>
+        <v>0.105636561034466</v>
       </c>
       <c r="T11">
-        <v>1.37034045692318</v>
+        <v>1.381906721350255</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.82072143320256</v>
+        <v>10.63864928988231</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09891646493101941</v>
+        <v>0.09883895483789477</v>
       </c>
       <c r="C12">
-        <v>363.9608527449604</v>
+        <v>360.5744020119539</v>
       </c>
       <c r="D12">
-        <v>402.0508527449605</v>
+        <v>402.6384020119539</v>
       </c>
       <c r="E12">
-        <v>15.54</v>
+        <v>19.514</v>
       </c>
       <c r="F12">
-        <v>39.74</v>
+        <v>43.714</v>
       </c>
       <c r="G12">
         <v>1.65</v>
@@ -2271,45 +2271,45 @@
         <v>21.9</v>
       </c>
       <c r="M12">
-        <v>2.058532</v>
+        <v>2.338699</v>
       </c>
       <c r="N12">
-        <v>19.841468</v>
+        <v>19.561301</v>
       </c>
       <c r="O12">
-        <v>5.119098744</v>
+        <v>5.046815658</v>
       </c>
       <c r="P12">
-        <v>14.722369256</v>
+        <v>14.514485342</v>
       </c>
       <c r="Q12">
-        <v>25.822369256</v>
+        <v>25.614485342</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.105636561034466</v>
+        <v>0.10614863464932</v>
       </c>
       <c r="T12">
-        <v>1.381906721350255</v>
+        <v>1.39373290183187</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.258</v>
       </c>
       <c r="W12">
-        <v>0.0384356</v>
+        <v>0.039697</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.6386492898823</v>
+        <v>9.364180683362845</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09883895483789477</v>
+        <v>0.09863530474477011</v>
       </c>
       <c r="C13">
-        <v>360.5744020119539</v>
+        <v>358.1523443819544</v>
       </c>
       <c r="D13">
-        <v>402.6384020119539</v>
+        <v>404.1903443819544</v>
       </c>
       <c r="E13">
-        <v>19.514</v>
+        <v>23.488</v>
       </c>
       <c r="F13">
-        <v>43.714</v>
+        <v>47.688</v>
       </c>
       <c r="G13">
         <v>1.65</v>
@@ -2353,28 +2353,28 @@
         <v>21.9</v>
       </c>
       <c r="M13">
-        <v>2.338699</v>
+        <v>2.551308</v>
       </c>
       <c r="N13">
-        <v>19.561301</v>
+        <v>19.348692</v>
       </c>
       <c r="O13">
-        <v>5.046815658</v>
+        <v>4.991962536</v>
       </c>
       <c r="P13">
-        <v>14.514485342</v>
+        <v>14.356729464</v>
       </c>
       <c r="Q13">
-        <v>25.614485342</v>
+        <v>25.456729464</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.10614863464932</v>
+        <v>0.1066723463008751</v>
       </c>
       <c r="T13">
-        <v>1.39373290183187</v>
+        <v>1.405827859142613</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.364180683362845</v>
+        <v>8.583832293082608</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09863530474477011</v>
+        <v>0.09843165465164548</v>
       </c>
       <c r="C14">
-        <v>358.1523443819544</v>
+        <v>355.7422967565904</v>
       </c>
       <c r="D14">
-        <v>404.1903443819544</v>
+        <v>405.7542967565904</v>
       </c>
       <c r="E14">
-        <v>23.488</v>
+        <v>27.462</v>
       </c>
       <c r="F14">
-        <v>47.688</v>
+        <v>51.662</v>
       </c>
       <c r="G14">
         <v>1.65</v>
@@ -2435,28 +2435,28 @@
         <v>21.9</v>
       </c>
       <c r="M14">
-        <v>2.551308</v>
+        <v>2.763917</v>
       </c>
       <c r="N14">
-        <v>19.348692</v>
+        <v>19.136083</v>
       </c>
       <c r="O14">
-        <v>4.991962536</v>
+        <v>4.937109414</v>
       </c>
       <c r="P14">
-        <v>14.356729464</v>
+        <v>14.198973586</v>
       </c>
       <c r="Q14">
-        <v>25.456729464</v>
+        <v>25.298973586</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1066723463008751</v>
+        <v>0.1072080973007419</v>
       </c>
       <c r="T14">
-        <v>1.405827859142613</v>
+        <v>1.418200861449006</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.583832293082608</v>
+        <v>7.923537501307022</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09843165465164548</v>
+        <v>0.09831110855852083</v>
       </c>
       <c r="C15">
-        <v>355.7422967565904</v>
+        <v>352.6997586240929</v>
       </c>
       <c r="D15">
-        <v>405.7542967565904</v>
+        <v>406.6857586240929</v>
       </c>
       <c r="E15">
-        <v>27.462</v>
+        <v>31.436</v>
       </c>
       <c r="F15">
-        <v>51.662</v>
+        <v>55.636</v>
       </c>
       <c r="G15">
         <v>1.65</v>
@@ -2517,45 +2517,45 @@
         <v>21.9</v>
       </c>
       <c r="M15">
-        <v>2.763917</v>
+        <v>3.0210348</v>
       </c>
       <c r="N15">
-        <v>19.136083</v>
+        <v>18.8789652</v>
       </c>
       <c r="O15">
-        <v>4.937109414</v>
+        <v>4.8707730216</v>
       </c>
       <c r="P15">
-        <v>14.198973586</v>
+        <v>14.0081921784</v>
       </c>
       <c r="Q15">
-        <v>25.298973586</v>
+        <v>25.1081921784</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1072080973007419</v>
+        <v>0.107756307626187</v>
       </c>
       <c r="T15">
-        <v>1.418200861449006</v>
+        <v>1.430861607995082</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.258</v>
       </c>
       <c r="W15">
-        <v>0.039697</v>
+        <v>0.0402906</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>7.923537501307022</v>
+        <v>7.249171707654608</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09831110855852083</v>
+        <v>0.0981133944653962</v>
       </c>
       <c r="C16">
-        <v>352.6997586240929</v>
+        <v>350.2627933887984</v>
       </c>
       <c r="D16">
-        <v>406.6857586240929</v>
+        <v>408.2227933887984</v>
       </c>
       <c r="E16">
-        <v>31.436</v>
+        <v>35.41000000000001</v>
       </c>
       <c r="F16">
-        <v>55.636</v>
+        <v>59.61000000000001</v>
       </c>
       <c r="G16">
         <v>1.65</v>
@@ -2599,28 +2599,28 @@
         <v>21.9</v>
       </c>
       <c r="M16">
-        <v>3.0210348</v>
+        <v>3.236823</v>
       </c>
       <c r="N16">
-        <v>18.8789652</v>
+        <v>18.663177</v>
       </c>
       <c r="O16">
-        <v>4.8707730216</v>
+        <v>4.815099665999999</v>
       </c>
       <c r="P16">
-        <v>14.0081921784</v>
+        <v>13.848077334</v>
       </c>
       <c r="Q16">
-        <v>25.1081921784</v>
+        <v>24.948077334</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.107756307626187</v>
+        <v>0.1083174170181132</v>
       </c>
       <c r="T16">
-        <v>1.430861607995082</v>
+        <v>1.443820254459889</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.249171707654608</v>
+        <v>6.765893593810967</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0981133944653962</v>
+        <v>0.09791568037227152</v>
       </c>
       <c r="C17">
-        <v>350.2627933887984</v>
+        <v>347.8374904183901</v>
       </c>
       <c r="D17">
-        <v>408.2227933887984</v>
+        <v>409.7714904183902</v>
       </c>
       <c r="E17">
-        <v>35.41</v>
+        <v>39.384</v>
       </c>
       <c r="F17">
-        <v>59.60999999999999</v>
+        <v>63.584</v>
       </c>
       <c r="G17">
         <v>1.65</v>
@@ -2681,28 +2681,28 @@
         <v>21.9</v>
       </c>
       <c r="M17">
-        <v>3.236823</v>
+        <v>3.4526112</v>
       </c>
       <c r="N17">
-        <v>18.663177</v>
+        <v>18.4473888</v>
       </c>
       <c r="O17">
-        <v>4.815099665999999</v>
+        <v>4.759426310399999</v>
       </c>
       <c r="P17">
-        <v>13.848077334</v>
+        <v>13.6879624896</v>
       </c>
       <c r="Q17">
-        <v>24.948077334</v>
+        <v>24.7879624896</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1083174170181132</v>
+        <v>0.1088918861574661</v>
       </c>
       <c r="T17">
-        <v>1.443820254459889</v>
+        <v>1.457087440126239</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.765893593810968</v>
+        <v>6.343025244197783</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09791568037227152</v>
+        <v>0.0978441062791469</v>
       </c>
       <c r="C18">
-        <v>347.8374904183901</v>
+        <v>344.4270320931709</v>
       </c>
       <c r="D18">
-        <v>409.7714904183902</v>
+        <v>410.3350320931709</v>
       </c>
       <c r="E18">
-        <v>39.384</v>
+        <v>43.358</v>
       </c>
       <c r="F18">
-        <v>63.584</v>
+        <v>67.55800000000001</v>
       </c>
       <c r="G18">
         <v>1.65</v>
@@ -2763,45 +2763,45 @@
         <v>21.9</v>
       </c>
       <c r="M18">
-        <v>3.4526112</v>
+        <v>3.735957400000001</v>
       </c>
       <c r="N18">
-        <v>18.4473888</v>
+        <v>18.1640426</v>
       </c>
       <c r="O18">
-        <v>4.759426310399999</v>
+        <v>4.6863229908</v>
       </c>
       <c r="P18">
-        <v>13.6879624896</v>
+        <v>13.4777196092</v>
       </c>
       <c r="Q18">
-        <v>24.7879624896</v>
+        <v>24.5777196092</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1088918861574661</v>
+        <v>0.109480197926683</v>
       </c>
       <c r="T18">
-        <v>1.457087440126239</v>
+        <v>1.470674317013465</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.258</v>
       </c>
       <c r="W18">
-        <v>0.0402906</v>
+        <v>0.0410326</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.343025244197783</v>
+        <v>5.861951209614969</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0978441062791469</v>
+        <v>0.09765381218602225</v>
       </c>
       <c r="C19">
-        <v>344.4270320931709</v>
+        <v>341.9588872948931</v>
       </c>
       <c r="D19">
-        <v>410.3350320931709</v>
+        <v>411.8408872948931</v>
       </c>
       <c r="E19">
-        <v>43.358</v>
+        <v>47.33200000000001</v>
       </c>
       <c r="F19">
-        <v>67.55800000000001</v>
+        <v>71.53200000000001</v>
       </c>
       <c r="G19">
         <v>1.65</v>
@@ -2845,28 +2845,28 @@
         <v>21.9</v>
       </c>
       <c r="M19">
-        <v>3.735957400000001</v>
+        <v>3.955719600000001</v>
       </c>
       <c r="N19">
-        <v>18.1640426</v>
+        <v>17.9442804</v>
       </c>
       <c r="O19">
-        <v>4.6863229908</v>
+        <v>4.6296243432</v>
       </c>
       <c r="P19">
-        <v>13.4777196092</v>
+        <v>13.3146560568</v>
       </c>
       <c r="Q19">
-        <v>24.5777196092</v>
+        <v>24.4146560568</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.109480197926683</v>
+        <v>0.1100828587634418</v>
       </c>
       <c r="T19">
-        <v>1.470674317013465</v>
+        <v>1.484592581141842</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.861951209614969</v>
+        <v>5.536287253525249</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09765381218602226</v>
+        <v>0.09746351809289762</v>
       </c>
       <c r="C20">
-        <v>341.958887294893</v>
+        <v>339.5018356377934</v>
       </c>
       <c r="D20">
-        <v>411.840887294893</v>
+        <v>413.3578356377935</v>
       </c>
       <c r="E20">
-        <v>47.33199999999999</v>
+        <v>51.306</v>
       </c>
       <c r="F20">
-        <v>71.532</v>
+        <v>75.506</v>
       </c>
       <c r="G20">
         <v>1.65</v>
@@ -2927,28 +2927,28 @@
         <v>21.9</v>
       </c>
       <c r="M20">
-        <v>3.9557196</v>
+        <v>4.1754818</v>
       </c>
       <c r="N20">
-        <v>17.9442804</v>
+        <v>17.7245182</v>
       </c>
       <c r="O20">
-        <v>4.6296243432</v>
+        <v>4.5729256956</v>
       </c>
       <c r="P20">
-        <v>13.3146560568</v>
+        <v>13.1515925044</v>
       </c>
       <c r="Q20">
-        <v>24.4146560568</v>
+        <v>24.2515925044</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1100828587634418</v>
+        <v>0.1107004001146884</v>
       </c>
       <c r="T20">
-        <v>1.484592581141842</v>
+        <v>1.498854506112896</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.536287253525249</v>
+        <v>5.244903713866026</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09746351809289762</v>
+        <v>0.09727322399977295</v>
       </c>
       <c r="C21">
-        <v>339.5018356377934</v>
+        <v>337.0560001543393</v>
       </c>
       <c r="D21">
-        <v>413.3578356377935</v>
+        <v>414.8860001543393</v>
       </c>
       <c r="E21">
-        <v>51.306</v>
+        <v>55.28</v>
       </c>
       <c r="F21">
-        <v>75.506</v>
+        <v>79.48</v>
       </c>
       <c r="G21">
         <v>1.65</v>
@@ -3009,28 +3009,28 @@
         <v>21.9</v>
       </c>
       <c r="M21">
-        <v>4.1754818</v>
+        <v>4.395244000000001</v>
       </c>
       <c r="N21">
-        <v>17.7245182</v>
+        <v>17.504756</v>
       </c>
       <c r="O21">
-        <v>4.5729256956</v>
+        <v>4.516227047999999</v>
       </c>
       <c r="P21">
-        <v>13.1515925044</v>
+        <v>12.988528952</v>
       </c>
       <c r="Q21">
-        <v>24.2515925044</v>
+        <v>24.088528952</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1107004001146884</v>
+        <v>0.1113333799997162</v>
       </c>
       <c r="T21">
-        <v>1.498854506112896</v>
+        <v>1.513472979208226</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.244903713866026</v>
+        <v>4.982658528172724</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09727322399977295</v>
+        <v>0.09708292990664832</v>
       </c>
       <c r="C22">
-        <v>337.0560001543393</v>
+        <v>334.6215057031289</v>
       </c>
       <c r="D22">
-        <v>414.8860001543393</v>
+        <v>416.425505703129</v>
       </c>
       <c r="E22">
-        <v>55.28</v>
+        <v>59.254</v>
       </c>
       <c r="F22">
-        <v>79.48</v>
+        <v>83.45400000000001</v>
       </c>
       <c r="G22">
         <v>1.65</v>
@@ -3091,28 +3091,28 @@
         <v>21.9</v>
       </c>
       <c r="M22">
-        <v>4.395244000000001</v>
+        <v>4.615006200000001</v>
       </c>
       <c r="N22">
-        <v>17.504756</v>
+        <v>17.2849938</v>
       </c>
       <c r="O22">
-        <v>4.516227047999999</v>
+        <v>4.4595284004</v>
       </c>
       <c r="P22">
-        <v>12.988528952</v>
+        <v>12.8254653996</v>
       </c>
       <c r="Q22">
-        <v>24.088528952</v>
+        <v>23.9254653996</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1113333799997162</v>
+        <v>0.1119823846919599</v>
       </c>
       <c r="T22">
-        <v>1.513472979208226</v>
+        <v>1.528461540230021</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.982658528172724</v>
+        <v>4.745389074450213</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0970829299066483</v>
+        <v>0.09689263581352366</v>
       </c>
       <c r="C23">
-        <v>334.6215057031291</v>
+        <v>332.198479002901</v>
       </c>
       <c r="D23">
-        <v>416.4255057031291</v>
+        <v>417.976479002901</v>
       </c>
       <c r="E23">
-        <v>59.25399999999999</v>
+        <v>63.22799999999999</v>
       </c>
       <c r="F23">
-        <v>83.45399999999999</v>
+        <v>87.428</v>
       </c>
       <c r="G23">
         <v>1.65</v>
@@ -3173,28 +3173,28 @@
         <v>21.9</v>
       </c>
       <c r="M23">
-        <v>4.6150062</v>
+        <v>4.8347684</v>
       </c>
       <c r="N23">
-        <v>17.2849938</v>
+        <v>17.0652316</v>
       </c>
       <c r="O23">
-        <v>4.4595284004</v>
+        <v>4.4028297528</v>
       </c>
       <c r="P23">
-        <v>12.8254653996</v>
+        <v>12.6624018472</v>
       </c>
       <c r="Q23">
-        <v>23.9254653996</v>
+        <v>23.7624018472</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1119823846919599</v>
+        <v>0.1126480305301585</v>
       </c>
       <c r="T23">
-        <v>1.528461540230021</v>
+        <v>1.543834423329297</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.745389074450214</v>
+        <v>4.529689571066113</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09689263581352366</v>
+        <v>0.09712899172039903</v>
       </c>
       <c r="C24">
-        <v>332.198479002901</v>
+        <v>326.2998121346048</v>
       </c>
       <c r="D24">
-        <v>417.976479002901</v>
+        <v>416.0518121346048</v>
       </c>
       <c r="E24">
-        <v>63.22799999999999</v>
+        <v>67.202</v>
       </c>
       <c r="F24">
-        <v>87.428</v>
+        <v>91.402</v>
       </c>
       <c r="G24">
         <v>1.65</v>
@@ -3255,45 +3255,45 @@
         <v>21.9</v>
       </c>
       <c r="M24">
-        <v>4.8347684</v>
+        <v>5.283035600000001</v>
       </c>
       <c r="N24">
-        <v>17.0652316</v>
+        <v>16.6169644</v>
       </c>
       <c r="O24">
-        <v>4.4028297528</v>
+        <v>4.2871768152</v>
       </c>
       <c r="P24">
-        <v>12.6624018472</v>
+        <v>12.3297875848</v>
       </c>
       <c r="Q24">
-        <v>23.7624018472</v>
+        <v>23.4297875848</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1126480305301585</v>
+        <v>0.1133309658706481</v>
       </c>
       <c r="T24">
-        <v>1.543834423329297</v>
+        <v>1.559606602093489</v>
       </c>
       <c r="U24">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V24">
         <v>0.258</v>
       </c>
       <c r="W24">
-        <v>0.0410326</v>
+        <v>0.0428876</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.529689571066113</v>
+        <v>4.145344013960457</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09712899172039903</v>
+        <v>0.09758052762727439</v>
       </c>
       <c r="C25">
-        <v>326.2998121346048</v>
+        <v>318.6977623462442</v>
       </c>
       <c r="D25">
-        <v>416.0518121346048</v>
+        <v>412.4237623462442</v>
       </c>
       <c r="E25">
-        <v>67.202</v>
+        <v>71.176</v>
       </c>
       <c r="F25">
-        <v>91.402</v>
+        <v>95.376</v>
       </c>
       <c r="G25">
         <v>1.65</v>
@@ -3337,45 +3337,45 @@
         <v>21.9</v>
       </c>
       <c r="M25">
-        <v>5.283035600000001</v>
+        <v>5.846548800000001</v>
       </c>
       <c r="N25">
-        <v>16.6169644</v>
+        <v>16.0534512</v>
       </c>
       <c r="O25">
-        <v>4.2871768152</v>
+        <v>4.1417904096</v>
       </c>
       <c r="P25">
-        <v>12.3297875848</v>
+        <v>11.9116607904</v>
       </c>
       <c r="Q25">
-        <v>23.4297875848</v>
+        <v>23.0116607904</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1133309658706481</v>
+        <v>0.1140318731937821</v>
       </c>
       <c r="T25">
-        <v>1.559606602093489</v>
+        <v>1.575793838193582</v>
       </c>
       <c r="U25">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V25">
         <v>0.258</v>
       </c>
       <c r="W25">
-        <v>0.0428876</v>
+        <v>0.0454846</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.145344013960457</v>
+        <v>3.745799573245672</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09758052762727439</v>
+        <v>0.09743475353414971</v>
       </c>
       <c r="C26">
-        <v>318.6977623462442</v>
+        <v>315.8881079821602</v>
       </c>
       <c r="D26">
-        <v>412.4237623462442</v>
+        <v>413.5881079821602</v>
       </c>
       <c r="E26">
-        <v>71.17599999999999</v>
+        <v>75.14999999999999</v>
       </c>
       <c r="F26">
-        <v>95.37599999999999</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="G26">
         <v>1.65</v>
@@ -3419,28 +3419,28 @@
         <v>21.9</v>
       </c>
       <c r="M26">
-        <v>5.8465488</v>
+        <v>6.090154999999999</v>
       </c>
       <c r="N26">
-        <v>16.0534512</v>
+        <v>15.809845</v>
       </c>
       <c r="O26">
-        <v>4.1417904096</v>
+        <v>4.07894001</v>
       </c>
       <c r="P26">
-        <v>11.9116607904</v>
+        <v>11.73090499</v>
       </c>
       <c r="Q26">
-        <v>23.0116607904</v>
+        <v>22.83090499</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1140318731937821</v>
+        <v>0.1147514713788663</v>
       </c>
       <c r="T26">
-        <v>1.575793838193582</v>
+        <v>1.59241273392301</v>
       </c>
       <c r="U26">
         <v>0.0613</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.745799573245673</v>
+        <v>3.595967590315846</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09743475353414971</v>
+        <v>0.09782915544102508</v>
       </c>
       <c r="C27">
-        <v>315.8881079821602</v>
+        <v>308.7789439175804</v>
       </c>
       <c r="D27">
-        <v>413.5881079821602</v>
+        <v>410.4529439175804</v>
       </c>
       <c r="E27">
-        <v>75.14999999999999</v>
+        <v>79.124</v>
       </c>
       <c r="F27">
-        <v>99.34999999999999</v>
+        <v>103.324</v>
       </c>
       <c r="G27">
         <v>1.65</v>
@@ -3501,45 +3501,45 @@
         <v>21.9</v>
       </c>
       <c r="M27">
-        <v>6.090154999999999</v>
+        <v>6.6230684</v>
       </c>
       <c r="N27">
-        <v>15.809845</v>
+        <v>15.2769316</v>
       </c>
       <c r="O27">
-        <v>4.07894001</v>
+        <v>3.941448352799999</v>
       </c>
       <c r="P27">
-        <v>11.73090499</v>
+        <v>11.3354832472</v>
       </c>
       <c r="Q27">
-        <v>22.83090499</v>
+        <v>22.4354832472</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1147514713788663</v>
+        <v>0.1154905181635474</v>
       </c>
       <c r="T27">
-        <v>1.59241273392301</v>
+        <v>1.609480788996476</v>
       </c>
       <c r="U27">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V27">
         <v>0.258</v>
       </c>
       <c r="W27">
-        <v>0.0454846</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.595967590315846</v>
+        <v>3.306624464273991</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09782915544102508</v>
+        <v>0.09770415734790044</v>
       </c>
       <c r="C28">
-        <v>308.7789439175804</v>
+        <v>305.7934164779421</v>
       </c>
       <c r="D28">
-        <v>410.4529439175804</v>
+        <v>411.4414164779421</v>
       </c>
       <c r="E28">
-        <v>79.124</v>
+        <v>83.098</v>
       </c>
       <c r="F28">
-        <v>103.324</v>
+        <v>107.298</v>
       </c>
       <c r="G28">
         <v>1.65</v>
@@ -3583,28 +3583,28 @@
         <v>21.9</v>
       </c>
       <c r="M28">
-        <v>6.6230684</v>
+        <v>6.8778018</v>
       </c>
       <c r="N28">
-        <v>15.2769316</v>
+        <v>15.0221982</v>
       </c>
       <c r="O28">
-        <v>3.941448352799999</v>
+        <v>3.8757271356</v>
       </c>
       <c r="P28">
-        <v>11.3354832472</v>
+        <v>11.1464710644</v>
       </c>
       <c r="Q28">
-        <v>22.4354832472</v>
+        <v>22.2464710644</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1154905181635474</v>
+        <v>0.1162498128053431</v>
       </c>
       <c r="T28">
-        <v>1.609480788996476</v>
+        <v>1.627016462017161</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.306624464273991</v>
+        <v>3.184156891523102</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09770415734790044</v>
+        <v>0.0975791592547758</v>
       </c>
       <c r="C29">
-        <v>305.7934164779421</v>
+        <v>302.8126615061047</v>
       </c>
       <c r="D29">
-        <v>411.4414164779421</v>
+        <v>412.4346615061047</v>
       </c>
       <c r="E29">
-        <v>83.098</v>
+        <v>87.072</v>
       </c>
       <c r="F29">
-        <v>107.298</v>
+        <v>111.272</v>
       </c>
       <c r="G29">
         <v>1.65</v>
@@ -3665,28 +3665,28 @@
         <v>21.9</v>
       </c>
       <c r="M29">
-        <v>6.8778018</v>
+        <v>7.1325352</v>
       </c>
       <c r="N29">
-        <v>15.0221982</v>
+        <v>14.7674648</v>
       </c>
       <c r="O29">
-        <v>3.8757271356</v>
+        <v>3.8100059184</v>
       </c>
       <c r="P29">
-        <v>11.1464710644</v>
+        <v>10.9574588816</v>
       </c>
       <c r="Q29">
-        <v>22.2464710644</v>
+        <v>22.0574588816</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1162498128053431</v>
+        <v>0.1170301989649664</v>
       </c>
       <c r="T29">
-        <v>1.627016462017161</v>
+        <v>1.645039237066198</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.184156891523102</v>
+        <v>3.070437002540134</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0975791592547758</v>
+        <v>0.09913256516165114</v>
       </c>
       <c r="C30">
-        <v>302.8126615061047</v>
+        <v>286.8257677433198</v>
       </c>
       <c r="D30">
-        <v>412.4346615061047</v>
+        <v>400.4217677433198</v>
       </c>
       <c r="E30">
-        <v>87.072</v>
+        <v>91.04600000000001</v>
       </c>
       <c r="F30">
-        <v>111.272</v>
+        <v>115.246</v>
       </c>
       <c r="G30">
         <v>1.65</v>
@@ -3747,45 +3747,45 @@
         <v>21.9</v>
       </c>
       <c r="M30">
-        <v>7.1325352</v>
+        <v>8.286187400000001</v>
       </c>
       <c r="N30">
-        <v>14.7674648</v>
+        <v>13.6138126</v>
       </c>
       <c r="O30">
-        <v>3.8100059184</v>
+        <v>3.512363650799999</v>
       </c>
       <c r="P30">
-        <v>10.9574588816</v>
+        <v>10.1014489492</v>
       </c>
       <c r="Q30">
-        <v>22.0574588816</v>
+        <v>21.2014489492</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1170301989649664</v>
+        <v>0.1178325678333115</v>
       </c>
       <c r="T30">
-        <v>1.645039237066198</v>
+        <v>1.663569695919434</v>
       </c>
       <c r="U30">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V30">
         <v>0.258</v>
       </c>
       <c r="W30">
-        <v>0.04756220000000001</v>
+        <v>0.0533498</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.070437002540134</v>
+        <v>2.642952535686074</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09913256516165114</v>
+        <v>0.09906544306852649</v>
       </c>
       <c r="C31">
-        <v>286.8257677433198</v>
+        <v>283.3563565655517</v>
       </c>
       <c r="D31">
-        <v>400.4217677433198</v>
+        <v>400.9263565655517</v>
       </c>
       <c r="E31">
-        <v>91.04599999999998</v>
+        <v>95.01999999999998</v>
       </c>
       <c r="F31">
-        <v>115.246</v>
+        <v>119.22</v>
       </c>
       <c r="G31">
         <v>1.65</v>
@@ -3829,28 +3829,28 @@
         <v>21.9</v>
       </c>
       <c r="M31">
-        <v>8.286187399999999</v>
+        <v>8.571918</v>
       </c>
       <c r="N31">
-        <v>13.6138126</v>
+        <v>13.328082</v>
       </c>
       <c r="O31">
-        <v>3.5123636508</v>
+        <v>3.438645156</v>
       </c>
       <c r="P31">
-        <v>10.1014489492</v>
+        <v>9.889436843999999</v>
       </c>
       <c r="Q31">
-        <v>21.2014489492</v>
+        <v>20.989436844</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1178325678333115</v>
+        <v>0.1186578615264664</v>
       </c>
       <c r="T31">
-        <v>1.663569695919434</v>
+        <v>1.68262959645419</v>
       </c>
       <c r="U31">
         <v>0.07190000000000001</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.642952535686074</v>
+        <v>2.554854117829872</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09906544306852649</v>
+        <v>0.09989539897540184</v>
       </c>
       <c r="C32">
-        <v>283.3563565655517</v>
+        <v>273.2311643356006</v>
       </c>
       <c r="D32">
-        <v>400.9263565655517</v>
+        <v>394.7751643356006</v>
       </c>
       <c r="E32">
-        <v>95.01999999999998</v>
+        <v>98.99399999999999</v>
       </c>
       <c r="F32">
-        <v>119.22</v>
+        <v>123.194</v>
       </c>
       <c r="G32">
         <v>1.65</v>
@@ -3911,45 +3911,45 @@
         <v>21.9</v>
       </c>
       <c r="M32">
-        <v>8.571918</v>
+        <v>9.338105199999999</v>
       </c>
       <c r="N32">
-        <v>13.328082</v>
+        <v>12.5618948</v>
       </c>
       <c r="O32">
-        <v>3.438645156</v>
+        <v>3.2409688584</v>
       </c>
       <c r="P32">
-        <v>9.889436843999999</v>
+        <v>9.320925941599999</v>
       </c>
       <c r="Q32">
-        <v>20.989436844</v>
+        <v>20.4209259416</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1186578615264664</v>
+        <v>0.1195070767759447</v>
       </c>
       <c r="T32">
-        <v>1.68262959645419</v>
+        <v>1.702241957874012</v>
       </c>
       <c r="U32">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V32">
         <v>0.258</v>
       </c>
       <c r="W32">
-        <v>0.0533498</v>
+        <v>0.0562436</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.554854117829872</v>
+        <v>2.345229522580234</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09989539897540184</v>
+        <v>0.0998572148822772</v>
       </c>
       <c r="C33">
-        <v>273.2311643356006</v>
+        <v>269.5360194647654</v>
       </c>
       <c r="D33">
-        <v>394.7751643356006</v>
+        <v>395.0540194647654</v>
       </c>
       <c r="E33">
-        <v>98.99399999999999</v>
+        <v>102.968</v>
       </c>
       <c r="F33">
-        <v>123.194</v>
+        <v>127.168</v>
       </c>
       <c r="G33">
         <v>1.65</v>
@@ -3993,28 +3993,28 @@
         <v>21.9</v>
       </c>
       <c r="M33">
-        <v>9.338105199999999</v>
+        <v>9.639334400000001</v>
       </c>
       <c r="N33">
-        <v>12.5618948</v>
+        <v>12.2606656</v>
       </c>
       <c r="O33">
-        <v>3.2409688584</v>
+        <v>3.163251724799999</v>
       </c>
       <c r="P33">
-        <v>9.320925941599999</v>
+        <v>9.097413875199997</v>
       </c>
       <c r="Q33">
-        <v>20.4209259416</v>
+        <v>20.1974138752</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1195070767759447</v>
+        <v>0.1203812689445253</v>
       </c>
       <c r="T33">
-        <v>1.702241957874012</v>
+        <v>1.722431153453241</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.345229522580234</v>
+        <v>2.271941099999601</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0998572148822772</v>
+        <v>0.09981903078915255</v>
       </c>
       <c r="C34">
-        <v>269.5360194647654</v>
+        <v>265.8412688190788</v>
       </c>
       <c r="D34">
-        <v>395.0540194647654</v>
+        <v>395.3332688190789</v>
       </c>
       <c r="E34">
-        <v>102.968</v>
+        <v>106.942</v>
       </c>
       <c r="F34">
-        <v>127.168</v>
+        <v>131.142</v>
       </c>
       <c r="G34">
         <v>1.65</v>
@@ -4075,28 +4075,28 @@
         <v>21.9</v>
       </c>
       <c r="M34">
-        <v>9.639334400000001</v>
+        <v>9.940563600000001</v>
       </c>
       <c r="N34">
-        <v>12.2606656</v>
+        <v>11.9594364</v>
       </c>
       <c r="O34">
-        <v>3.163251724799999</v>
+        <v>3.0855345912</v>
       </c>
       <c r="P34">
-        <v>9.097413875199997</v>
+        <v>8.873901808799998</v>
       </c>
       <c r="Q34">
-        <v>20.1974138752</v>
+        <v>19.9739018088</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1203812689445253</v>
+        <v>0.1212815564017202</v>
       </c>
       <c r="T34">
-        <v>1.722431153453241</v>
+        <v>1.743223011587073</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.271941099999601</v>
+        <v>2.203094399999613</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09981903078915255</v>
+        <v>0.09978084669602791</v>
       </c>
       <c r="C35">
-        <v>265.8412688190788</v>
+        <v>262.1469132351226</v>
       </c>
       <c r="D35">
-        <v>395.3332688190789</v>
+        <v>395.6129132351226</v>
       </c>
       <c r="E35">
-        <v>106.942</v>
+        <v>110.916</v>
       </c>
       <c r="F35">
-        <v>131.142</v>
+        <v>135.116</v>
       </c>
       <c r="G35">
         <v>1.65</v>
@@ -4157,28 +4157,28 @@
         <v>21.9</v>
       </c>
       <c r="M35">
-        <v>9.940563600000001</v>
+        <v>10.2417928</v>
       </c>
       <c r="N35">
-        <v>11.9594364</v>
+        <v>11.6582072</v>
       </c>
       <c r="O35">
-        <v>3.0855345912</v>
+        <v>3.007817457599999</v>
       </c>
       <c r="P35">
-        <v>8.873901808799998</v>
+        <v>8.650389742399998</v>
       </c>
       <c r="Q35">
-        <v>19.9739018088</v>
+        <v>19.7503897424</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1212815564017202</v>
+        <v>0.122209125297012</v>
       </c>
       <c r="T35">
-        <v>1.743223011587073</v>
+        <v>1.764644926027991</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.203094399999613</v>
+        <v>2.138297505881977</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09978084669602791</v>
+        <v>0.09974266260290326</v>
       </c>
       <c r="C36">
-        <v>262.1469132351226</v>
+        <v>258.452953551847</v>
       </c>
       <c r="D36">
-        <v>395.6129132351226</v>
+        <v>395.8929535518471</v>
       </c>
       <c r="E36">
-        <v>110.916</v>
+        <v>114.89</v>
       </c>
       <c r="F36">
-        <v>135.116</v>
+        <v>139.09</v>
       </c>
       <c r="G36">
         <v>1.65</v>
@@ -4239,28 +4239,28 @@
         <v>21.9</v>
       </c>
       <c r="M36">
-        <v>10.2417928</v>
+        <v>10.543022</v>
       </c>
       <c r="N36">
-        <v>11.6582072</v>
+        <v>11.356978</v>
       </c>
       <c r="O36">
-        <v>3.007817457599999</v>
+        <v>2.930100324</v>
       </c>
       <c r="P36">
-        <v>8.650389742399998</v>
+        <v>8.426877675999998</v>
       </c>
       <c r="Q36">
-        <v>19.7503897424</v>
+        <v>19.526877676</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.122209125297012</v>
+        <v>0.1231652347736973</v>
       </c>
       <c r="T36">
-        <v>1.764644926027991</v>
+        <v>1.78672597629786</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.138297505881977</v>
+        <v>2.077203291428207</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09974266260290326</v>
+        <v>0.09970447850977859</v>
       </c>
       <c r="C37">
-        <v>258.452953551847</v>
+        <v>254.7593906105802</v>
       </c>
       <c r="D37">
-        <v>395.8929535518471</v>
+        <v>396.1733906105802</v>
       </c>
       <c r="E37">
-        <v>114.89</v>
+        <v>118.864</v>
       </c>
       <c r="F37">
-        <v>139.09</v>
+        <v>143.064</v>
       </c>
       <c r="G37">
         <v>1.65</v>
@@ -4321,28 +4321,28 @@
         <v>21.9</v>
       </c>
       <c r="M37">
-        <v>10.543022</v>
+        <v>10.8442512</v>
       </c>
       <c r="N37">
-        <v>11.356978</v>
+        <v>11.0557488</v>
       </c>
       <c r="O37">
-        <v>2.930100324</v>
+        <v>2.852383190399999</v>
       </c>
       <c r="P37">
-        <v>8.426877675999998</v>
+        <v>8.203365609599997</v>
       </c>
       <c r="Q37">
-        <v>19.526877676</v>
+        <v>19.3033656096</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1231652347736973</v>
+        <v>0.1241512226715291</v>
       </c>
       <c r="T37">
-        <v>1.78672597629786</v>
+        <v>1.809497059388663</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.077203291428207</v>
+        <v>2.019503199999646</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09970447850977862</v>
+        <v>0.103564762416654</v>
       </c>
       <c r="C38">
-        <v>254.75939061058</v>
+        <v>224.3100499335906</v>
       </c>
       <c r="D38">
-        <v>396.17339061058</v>
+        <v>369.6980499335906</v>
       </c>
       <c r="E38">
-        <v>118.864</v>
+        <v>122.838</v>
       </c>
       <c r="F38">
-        <v>143.064</v>
+        <v>147.038</v>
       </c>
       <c r="G38">
         <v>1.65</v>
@@ -4403,45 +4403,45 @@
         <v>21.9</v>
       </c>
       <c r="M38">
-        <v>10.8442512</v>
+        <v>13.23342</v>
       </c>
       <c r="N38">
-        <v>11.0557488</v>
+        <v>8.666580000000002</v>
       </c>
       <c r="O38">
-        <v>2.852383190399999</v>
+        <v>2.235977640000001</v>
       </c>
       <c r="P38">
-        <v>8.203365609599999</v>
+        <v>6.430602360000001</v>
       </c>
       <c r="Q38">
-        <v>19.3033656096</v>
+        <v>17.53060236</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1241512226715291</v>
+        <v>0.1251685117724666</v>
       </c>
       <c r="T38">
-        <v>1.809497059388663</v>
+        <v>1.832991034006158</v>
       </c>
       <c r="U38">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V38">
         <v>0.258</v>
       </c>
       <c r="W38">
-        <v>0.0562436</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.019503199999646</v>
+        <v>1.654901000648359</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.103564762416654</v>
+        <v>0.1036319423235293</v>
       </c>
       <c r="C39">
-        <v>224.3100499335906</v>
+        <v>219.9065938308092</v>
       </c>
       <c r="D39">
-        <v>369.6980499335906</v>
+        <v>369.2685938308093</v>
       </c>
       <c r="E39">
-        <v>122.838</v>
+        <v>126.812</v>
       </c>
       <c r="F39">
-        <v>147.038</v>
+        <v>151.012</v>
       </c>
       <c r="G39">
         <v>1.65</v>
@@ -4485,28 +4485,28 @@
         <v>21.9</v>
       </c>
       <c r="M39">
-        <v>13.23342</v>
+        <v>13.59108</v>
       </c>
       <c r="N39">
-        <v>8.666580000000002</v>
+        <v>8.308919999999999</v>
       </c>
       <c r="O39">
-        <v>2.235977640000001</v>
+        <v>2.14370136</v>
       </c>
       <c r="P39">
-        <v>6.430602360000001</v>
+        <v>6.165218639999999</v>
       </c>
       <c r="Q39">
-        <v>17.53060236</v>
+        <v>17.26521864</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1251685117724666</v>
+        <v>0.1262186166508538</v>
       </c>
       <c r="T39">
-        <v>1.832991034006158</v>
+        <v>1.857242878772605</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.654901000648359</v>
+        <v>1.611350974315507</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1036319423235293</v>
+        <v>0.1036991222304047</v>
       </c>
       <c r="C40">
-        <v>219.9065938308092</v>
+        <v>215.5041343172639</v>
       </c>
       <c r="D40">
-        <v>369.2685938308093</v>
+        <v>368.840134317264</v>
       </c>
       <c r="E40">
-        <v>126.812</v>
+        <v>130.786</v>
       </c>
       <c r="F40">
-        <v>151.012</v>
+        <v>154.986</v>
       </c>
       <c r="G40">
         <v>1.65</v>
@@ -4567,28 +4567,28 @@
         <v>21.9</v>
       </c>
       <c r="M40">
-        <v>13.59108</v>
+        <v>13.94874</v>
       </c>
       <c r="N40">
-        <v>8.308919999999999</v>
+        <v>7.95126</v>
       </c>
       <c r="O40">
-        <v>2.14370136</v>
+        <v>2.05142508</v>
       </c>
       <c r="P40">
-        <v>6.165218639999999</v>
+        <v>5.89983492</v>
       </c>
       <c r="Q40">
-        <v>17.26521864</v>
+        <v>16.99983492</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1262186166508538</v>
+        <v>0.1273031511973847</v>
       </c>
       <c r="T40">
-        <v>1.857242878772605</v>
+        <v>1.88228986599041</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.611350974315507</v>
+        <v>1.570034282666391</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1036991222304047</v>
+        <v>0.10376630213728</v>
       </c>
       <c r="C41">
-        <v>215.5041343172639</v>
+        <v>211.1026679279702</v>
       </c>
       <c r="D41">
-        <v>368.840134317264</v>
+        <v>368.4126679279702</v>
       </c>
       <c r="E41">
-        <v>130.786</v>
+        <v>134.76</v>
       </c>
       <c r="F41">
-        <v>154.986</v>
+        <v>158.96</v>
       </c>
       <c r="G41">
         <v>1.65</v>
@@ -4649,28 +4649,28 @@
         <v>21.9</v>
       </c>
       <c r="M41">
-        <v>13.94874</v>
+        <v>14.3064</v>
       </c>
       <c r="N41">
-        <v>7.95126</v>
+        <v>7.593599999999999</v>
       </c>
       <c r="O41">
-        <v>2.05142508</v>
+        <v>1.9591488</v>
       </c>
       <c r="P41">
-        <v>5.89983492</v>
+        <v>5.634451199999999</v>
       </c>
       <c r="Q41">
-        <v>16.99983492</v>
+        <v>16.7344512</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1273031511973847</v>
+        <v>0.1284238368954667</v>
       </c>
       <c r="T41">
-        <v>1.88228986599041</v>
+        <v>1.908171752782142</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.570034282666391</v>
+        <v>1.530783425599731</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.10376630213728</v>
+        <v>0.1229172813060741</v>
       </c>
       <c r="C42">
-        <v>211.1026679279702</v>
+        <v>115.6386256246676</v>
       </c>
       <c r="D42">
-        <v>368.4126679279702</v>
+        <v>276.9226256246677</v>
       </c>
       <c r="E42">
-        <v>134.76</v>
+        <v>138.734</v>
       </c>
       <c r="F42">
-        <v>158.96</v>
+        <v>162.934</v>
       </c>
       <c r="G42">
         <v>1.65</v>
@@ -4731,45 +4731,45 @@
         <v>21.9</v>
       </c>
       <c r="M42">
-        <v>14.3064</v>
+        <v>23.9187112</v>
       </c>
       <c r="N42">
-        <v>7.593599999999999</v>
+        <v>-2.018711200000002</v>
       </c>
       <c r="O42">
-        <v>1.9591488</v>
+        <v>-0.5208274896000006</v>
       </c>
       <c r="P42">
-        <v>5.634451199999999</v>
+        <v>-1.497883710400001</v>
       </c>
       <c r="Q42">
-        <v>16.7344512</v>
+        <v>9.602116289599998</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1284238368954667</v>
+        <v>0.1304189792593973</v>
       </c>
       <c r="T42">
-        <v>1.908171752782142</v>
+        <v>1.954248943635041</v>
       </c>
       <c r="U42">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.258</v>
+        <v>0.2362251022956454</v>
       </c>
       <c r="W42">
-        <v>0.06677999999999999</v>
+        <v>0.1121221549829993</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y42">
-        <v>1.530783425599731</v>
+        <v>0.915601171688548</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1229172813060741</v>
+        <v>0.1239272813060741</v>
       </c>
       <c r="C43">
-        <v>115.6386256246676</v>
+        <v>108.0846744577356</v>
       </c>
       <c r="D43">
-        <v>276.9226256246677</v>
+        <v>273.3426744577356</v>
       </c>
       <c r="E43">
-        <v>138.734</v>
+        <v>142.708</v>
       </c>
       <c r="F43">
-        <v>162.934</v>
+        <v>166.908</v>
       </c>
       <c r="G43">
         <v>1.65</v>
@@ -4813,37 +4813,37 @@
         <v>21.9</v>
       </c>
       <c r="M43">
-        <v>23.9187112</v>
+        <v>24.5020944</v>
       </c>
       <c r="N43">
-        <v>-2.018711200000002</v>
+        <v>-2.602094400000006</v>
       </c>
       <c r="O43">
-        <v>-0.5208274896000006</v>
+        <v>-0.6713403552000015</v>
       </c>
       <c r="P43">
-        <v>-1.497883710400001</v>
+        <v>-1.930754044800004</v>
       </c>
       <c r="Q43">
-        <v>9.602116289599998</v>
+        <v>9.169245955199996</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1304189792593973</v>
+        <v>0.1318779271776628</v>
       </c>
       <c r="T43">
-        <v>1.954248943635041</v>
+        <v>1.987942890939094</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.2362251022956454</v>
+        <v>0.23060069509813</v>
       </c>
       <c r="W43">
-        <v>0.1121221549829993</v>
+        <v>0.1129478179595945</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.915601171688548</v>
+        <v>0.8938011437912016</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1239272813060741</v>
+        <v>0.1249372813060741</v>
       </c>
       <c r="C44">
-        <v>108.0846744577356</v>
+        <v>100.622102489556</v>
       </c>
       <c r="D44">
-        <v>273.3426744577356</v>
+        <v>269.854102489556</v>
       </c>
       <c r="E44">
-        <v>142.708</v>
+        <v>146.682</v>
       </c>
       <c r="F44">
-        <v>166.908</v>
+        <v>170.882</v>
       </c>
       <c r="G44">
         <v>1.65</v>
@@ -4895,37 +4895,37 @@
         <v>21.9</v>
       </c>
       <c r="M44">
-        <v>24.5020944</v>
+        <v>25.0854776</v>
       </c>
       <c r="N44">
-        <v>-2.602094400000002</v>
+        <v>-3.185477599999999</v>
       </c>
       <c r="O44">
-        <v>-0.6713403552000006</v>
+        <v>-0.8218532207999997</v>
       </c>
       <c r="P44">
-        <v>-1.930754044800002</v>
+        <v>-2.363624379199999</v>
       </c>
       <c r="Q44">
-        <v>9.169245955199997</v>
+        <v>8.736375620800001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1318779271776628</v>
+        <v>0.1333880662509551</v>
       </c>
       <c r="T44">
-        <v>1.987942890939094</v>
+        <v>2.0228190820082</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.23060069509813</v>
+        <v>0.2252378882353829</v>
       </c>
       <c r="W44">
-        <v>0.1129478179595945</v>
+        <v>0.1137350780070458</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8938011437912017</v>
+        <v>0.8730150706797786</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1249372813060741</v>
+        <v>0.1259472813060741</v>
       </c>
       <c r="C45">
-        <v>100.622102489556</v>
+        <v>93.24745509300107</v>
       </c>
       <c r="D45">
-        <v>269.854102489556</v>
+        <v>266.4534550930011</v>
       </c>
       <c r="E45">
-        <v>146.682</v>
+        <v>150.656</v>
       </c>
       <c r="F45">
-        <v>170.882</v>
+        <v>174.856</v>
       </c>
       <c r="G45">
         <v>1.65</v>
@@ -4977,37 +4977,37 @@
         <v>21.9</v>
       </c>
       <c r="M45">
-        <v>25.0854776</v>
+        <v>25.6688608</v>
       </c>
       <c r="N45">
-        <v>-3.185477599999999</v>
+        <v>-3.768860800000002</v>
       </c>
       <c r="O45">
-        <v>-0.8218532207999997</v>
+        <v>-0.9723660864000007</v>
       </c>
       <c r="P45">
-        <v>-2.363624379199999</v>
+        <v>-2.796494713600002</v>
       </c>
       <c r="Q45">
-        <v>8.736375620800001</v>
+        <v>8.303505286399998</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1333880662509551</v>
+        <v>0.1349521388625793</v>
       </c>
       <c r="T45">
-        <v>2.0228190820082</v>
+        <v>2.058940851329776</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.2252378882353829</v>
+        <v>0.2201188453209423</v>
       </c>
       <c r="W45">
-        <v>0.1137350780070458</v>
+        <v>0.1144865535068857</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8730150706797786</v>
+        <v>0.8531738190734198</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1259472813060741</v>
+        <v>0.1269572813060741</v>
       </c>
       <c r="C46">
-        <v>93.24745509300107</v>
+        <v>85.95744961187876</v>
       </c>
       <c r="D46">
-        <v>266.4534550930011</v>
+        <v>263.1374496118788</v>
       </c>
       <c r="E46">
-        <v>150.656</v>
+        <v>154.63</v>
       </c>
       <c r="F46">
-        <v>174.856</v>
+        <v>178.83</v>
       </c>
       <c r="G46">
         <v>1.65</v>
@@ -5059,37 +5059,37 @@
         <v>21.9</v>
       </c>
       <c r="M46">
-        <v>25.6688608</v>
+        <v>26.252244</v>
       </c>
       <c r="N46">
-        <v>-3.768860800000002</v>
+        <v>-4.352244000000002</v>
       </c>
       <c r="O46">
-        <v>-0.9723660864000007</v>
+        <v>-1.122878952000001</v>
       </c>
       <c r="P46">
-        <v>-2.796494713600002</v>
+        <v>-3.229365048000002</v>
       </c>
       <c r="Q46">
-        <v>8.303505286399998</v>
+        <v>7.870634951999998</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1349521388625793</v>
+        <v>0.1365730868418989</v>
       </c>
       <c r="T46">
-        <v>2.058940851329776</v>
+        <v>2.096376139535772</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.2201188453209423</v>
+        <v>0.2152273154249214</v>
       </c>
       <c r="W46">
-        <v>0.1144865535068857</v>
+        <v>0.1152046300956216</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8531738190734198</v>
+        <v>0.8342144008717882</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1269572813060741</v>
+        <v>0.1279672813060741</v>
       </c>
       <c r="C47">
-        <v>85.95744961187876</v>
+        <v>78.74896479160086</v>
       </c>
       <c r="D47">
-        <v>263.1374496118788</v>
+        <v>259.9029647916009</v>
       </c>
       <c r="E47">
-        <v>154.63</v>
+        <v>158.604</v>
       </c>
       <c r="F47">
-        <v>178.83</v>
+        <v>182.804</v>
       </c>
       <c r="G47">
         <v>1.65</v>
@@ -5141,37 +5141,37 @@
         <v>21.9</v>
       </c>
       <c r="M47">
-        <v>26.252244</v>
+        <v>26.8356272</v>
       </c>
       <c r="N47">
-        <v>-4.352244000000002</v>
+        <v>-4.935627200000003</v>
       </c>
       <c r="O47">
-        <v>-1.122878952000001</v>
+        <v>-1.273391817600001</v>
       </c>
       <c r="P47">
-        <v>-3.229365048000002</v>
+        <v>-3.662235382400002</v>
       </c>
       <c r="Q47">
-        <v>7.870634951999998</v>
+        <v>7.437764617599997</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1365730868418989</v>
+        <v>0.1382540699315637</v>
       </c>
       <c r="T47">
-        <v>2.096376139535772</v>
+        <v>2.135197919897545</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.2152273154249214</v>
+        <v>0.2105484607417709</v>
       </c>
       <c r="W47">
-        <v>0.1152046300956216</v>
+        <v>0.115891485963108</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8342144008717882</v>
+        <v>0.8160793052006624</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1279672813060741</v>
+        <v>0.1557970773088528</v>
       </c>
       <c r="C48">
-        <v>78.74896479160086</v>
+        <v>9.018249543990436</v>
       </c>
       <c r="D48">
-        <v>259.9029647916009</v>
+        <v>194.1462495439904</v>
       </c>
       <c r="E48">
-        <v>158.604</v>
+        <v>162.578</v>
       </c>
       <c r="F48">
-        <v>182.804</v>
+        <v>186.778</v>
       </c>
       <c r="G48">
         <v>1.65</v>
@@ -5223,45 +5223,45 @@
         <v>21.9</v>
       </c>
       <c r="M48">
-        <v>26.8356272</v>
+        <v>37.5050224</v>
       </c>
       <c r="N48">
-        <v>-4.935627200000003</v>
+        <v>-15.6050224</v>
       </c>
       <c r="O48">
-        <v>-1.273391817600001</v>
+        <v>-4.026095779200001</v>
       </c>
       <c r="P48">
-        <v>-3.662235382400002</v>
+        <v>-11.5789266208</v>
       </c>
       <c r="Q48">
-        <v>7.437764617599997</v>
+        <v>-0.4789266208000011</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1382540699315637</v>
+        <v>0.1427150825770247</v>
       </c>
       <c r="T48">
-        <v>2.135197919897545</v>
+        <v>2.238223616097568</v>
       </c>
       <c r="U48">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.2105484607417709</v>
+        <v>0.1506518231008975</v>
       </c>
       <c r="W48">
-        <v>0.115891485963108</v>
+        <v>0.1705491139213398</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.8160793052006624</v>
+        <v>0.5839217949647191</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1557970773088528</v>
+        <v>0.1573470773088528</v>
       </c>
       <c r="C49">
-        <v>9.018249543990436</v>
+        <v>2.346494532803803</v>
       </c>
       <c r="D49">
-        <v>194.1462495439904</v>
+        <v>191.4484945328038</v>
       </c>
       <c r="E49">
-        <v>162.578</v>
+        <v>166.552</v>
       </c>
       <c r="F49">
-        <v>186.778</v>
+        <v>190.752</v>
       </c>
       <c r="G49">
         <v>1.65</v>
@@ -5305,37 +5305,37 @@
         <v>21.9</v>
       </c>
       <c r="M49">
-        <v>37.5050224</v>
+        <v>38.3030016</v>
       </c>
       <c r="N49">
-        <v>-15.6050224</v>
+        <v>-16.4030016</v>
       </c>
       <c r="O49">
-        <v>-4.026095779200001</v>
+        <v>-4.231974412800001</v>
       </c>
       <c r="P49">
-        <v>-11.5789266208</v>
+        <v>-12.1710271872</v>
       </c>
       <c r="Q49">
-        <v>-0.4789266208000011</v>
+        <v>-1.071027187200004</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1427150825770247</v>
+        <v>0.1445788341650444</v>
       </c>
       <c r="T49">
-        <v>2.238223616097568</v>
+        <v>2.281266377945598</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1506518231008975</v>
+        <v>0.1475132434529622</v>
       </c>
       <c r="W49">
-        <v>0.1705491139213398</v>
+        <v>0.1711793407146452</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5839217949647191</v>
+        <v>0.5717567575696207</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1573470773088528</v>
+        <v>0.1588970773088528</v>
       </c>
       <c r="C50">
-        <v>2.346494532803831</v>
+        <v>-4.251314796198386</v>
       </c>
       <c r="D50">
-        <v>191.4484945328038</v>
+        <v>188.8246852038016</v>
       </c>
       <c r="E50">
-        <v>166.552</v>
+        <v>170.526</v>
       </c>
       <c r="F50">
-        <v>190.752</v>
+        <v>194.726</v>
       </c>
       <c r="G50">
         <v>1.65</v>
@@ -5387,37 +5387,37 @@
         <v>21.9</v>
       </c>
       <c r="M50">
-        <v>38.30300159999999</v>
+        <v>39.1009808</v>
       </c>
       <c r="N50">
-        <v>-16.4030016</v>
+        <v>-17.2009808</v>
       </c>
       <c r="O50">
-        <v>-4.231974412799999</v>
+        <v>-4.437853046400001</v>
       </c>
       <c r="P50">
-        <v>-12.1710271872</v>
+        <v>-12.7631277536</v>
       </c>
       <c r="Q50">
-        <v>-1.071027187199997</v>
+        <v>-1.663127753600003</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1445788341650444</v>
+        <v>0.1465156740506335</v>
       </c>
       <c r="T50">
-        <v>2.281266377945598</v>
+        <v>2.325997091238649</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1475132434529622</v>
+        <v>0.1445027690967793</v>
       </c>
       <c r="W50">
-        <v>0.1711793407146452</v>
+        <v>0.1717838439653667</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.571756757569621</v>
+        <v>0.5600882523130979</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1588970773088528</v>
+        <v>0.1604470773088528</v>
       </c>
       <c r="C51">
-        <v>-4.251314796198386</v>
+        <v>-10.77817762476775</v>
       </c>
       <c r="D51">
-        <v>188.8246852038016</v>
+        <v>186.2718223752322</v>
       </c>
       <c r="E51">
-        <v>170.526</v>
+        <v>174.5</v>
       </c>
       <c r="F51">
-        <v>194.726</v>
+        <v>198.7</v>
       </c>
       <c r="G51">
         <v>1.65</v>
@@ -5469,37 +5469,37 @@
         <v>21.9</v>
       </c>
       <c r="M51">
-        <v>39.1009808</v>
+        <v>39.89896</v>
       </c>
       <c r="N51">
-        <v>-17.2009808</v>
+        <v>-17.99896</v>
       </c>
       <c r="O51">
-        <v>-4.437853046400001</v>
+        <v>-4.643731680000001</v>
       </c>
       <c r="P51">
-        <v>-12.7631277536</v>
+        <v>-13.35522832</v>
       </c>
       <c r="Q51">
-        <v>-1.663127753600003</v>
+        <v>-2.255228320000002</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1465156740506335</v>
+        <v>0.1485299875316461</v>
       </c>
       <c r="T51">
-        <v>2.325997091238649</v>
+        <v>2.372517033063422</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1445027690967793</v>
+        <v>0.1416127137148437</v>
       </c>
       <c r="W51">
-        <v>0.1717838439653667</v>
+        <v>0.1723641670860594</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5600882523130979</v>
+        <v>0.548886487266836</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1604470773088528</v>
+        <v>0.1619970773088528</v>
       </c>
       <c r="C52">
-        <v>-10.77817762476775</v>
+        <v>-17.23693310544292</v>
       </c>
       <c r="D52">
-        <v>186.2718223752322</v>
+        <v>183.7870668945571</v>
       </c>
       <c r="E52">
-        <v>174.5</v>
+        <v>178.474</v>
       </c>
       <c r="F52">
-        <v>198.7</v>
+        <v>202.674</v>
       </c>
       <c r="G52">
         <v>1.65</v>
@@ -5551,37 +5551,37 @@
         <v>21.9</v>
       </c>
       <c r="M52">
-        <v>39.89896</v>
+        <v>40.6969392</v>
       </c>
       <c r="N52">
-        <v>-17.99896</v>
+        <v>-18.7969392</v>
       </c>
       <c r="O52">
-        <v>-4.643731680000001</v>
+        <v>-4.8496103136</v>
       </c>
       <c r="P52">
-        <v>-13.35522832</v>
+        <v>-13.9473288864</v>
       </c>
       <c r="Q52">
-        <v>-2.255228320000002</v>
+        <v>-2.847328886399998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1485299875316461</v>
+        <v>0.1506265178894348</v>
       </c>
       <c r="T52">
-        <v>2.372517033063422</v>
+        <v>2.4209357480239</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1416127137148437</v>
+        <v>0.1388359938380821</v>
       </c>
       <c r="W52">
-        <v>0.1723641670860594</v>
+        <v>0.1729217324373131</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.548886487266836</v>
+        <v>0.538124007124349</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1619970773088528</v>
+        <v>0.1635470773088528</v>
       </c>
       <c r="C53">
-        <v>-17.23693310544292</v>
+        <v>-23.63027089451896</v>
       </c>
       <c r="D53">
-        <v>183.7870668945571</v>
+        <v>181.367729105481</v>
       </c>
       <c r="E53">
-        <v>178.474</v>
+        <v>182.448</v>
       </c>
       <c r="F53">
-        <v>202.674</v>
+        <v>206.648</v>
       </c>
       <c r="G53">
         <v>1.65</v>
@@ -5633,37 +5633,37 @@
         <v>21.9</v>
       </c>
       <c r="M53">
-        <v>40.6969392</v>
+        <v>41.4949184</v>
       </c>
       <c r="N53">
-        <v>-18.7969392</v>
+        <v>-19.5949184</v>
       </c>
       <c r="O53">
-        <v>-4.8496103136</v>
+        <v>-5.055488947200002</v>
       </c>
       <c r="P53">
-        <v>-13.9473288864</v>
+        <v>-14.5394294528</v>
       </c>
       <c r="Q53">
-        <v>-2.847328886399998</v>
+        <v>-3.439429452800004</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1506265178894348</v>
+        <v>0.1528104036787981</v>
       </c>
       <c r="T53">
-        <v>2.4209357480239</v>
+        <v>2.471371909441065</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1388359938380821</v>
+        <v>0.1361660708796574</v>
       </c>
       <c r="W53">
-        <v>0.1729217324373131</v>
+        <v>0.1734578529673648</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.538124007124349</v>
+        <v>0.5277754685258038</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1635470773088528</v>
+        <v>0.1650970773088528</v>
       </c>
       <c r="C54">
-        <v>-23.63027089451896</v>
+        <v>-29.96074086390212</v>
       </c>
       <c r="D54">
-        <v>181.367729105481</v>
+        <v>179.0112591360979</v>
       </c>
       <c r="E54">
-        <v>182.448</v>
+        <v>186.422</v>
       </c>
       <c r="F54">
-        <v>206.648</v>
+        <v>210.622</v>
       </c>
       <c r="G54">
         <v>1.65</v>
@@ -5715,37 +5715,37 @@
         <v>21.9</v>
       </c>
       <c r="M54">
-        <v>41.4949184</v>
+        <v>42.2928976</v>
       </c>
       <c r="N54">
-        <v>-19.5949184</v>
+        <v>-20.3928976</v>
       </c>
       <c r="O54">
-        <v>-5.055488947200002</v>
+        <v>-5.2613675808</v>
       </c>
       <c r="P54">
-        <v>-14.5394294528</v>
+        <v>-15.1315300192</v>
       </c>
       <c r="Q54">
-        <v>-3.439429452800004</v>
+        <v>-4.031530019199998</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1528104036787981</v>
+        <v>0.155087220778347</v>
       </c>
       <c r="T54">
-        <v>2.471371909441065</v>
+        <v>2.523954290493002</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1361660708796574</v>
+        <v>0.1335968997309846</v>
       </c>
       <c r="W54">
-        <v>0.1734578529673648</v>
+        <v>0.1739737425340183</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5277754685258038</v>
+        <v>0.5178174408177698</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1650970773088528</v>
+        <v>0.1666470773088528</v>
       </c>
       <c r="C55">
-        <v>-29.96074086390212</v>
+        <v>-36.23076206557195</v>
       </c>
       <c r="D55">
-        <v>179.0112591360979</v>
+        <v>176.715237934428</v>
       </c>
       <c r="E55">
-        <v>186.422</v>
+        <v>190.396</v>
       </c>
       <c r="F55">
-        <v>210.622</v>
+        <v>214.596</v>
       </c>
       <c r="G55">
         <v>1.65</v>
@@ -5797,37 +5797,37 @@
         <v>21.9</v>
       </c>
       <c r="M55">
-        <v>42.2928976</v>
+        <v>43.0908768</v>
       </c>
       <c r="N55">
-        <v>-20.3928976</v>
+        <v>-21.19087680000001</v>
       </c>
       <c r="O55">
-        <v>-5.2613675808</v>
+        <v>-5.467246214400001</v>
       </c>
       <c r="P55">
-        <v>-15.1315300192</v>
+        <v>-15.7236305856</v>
       </c>
       <c r="Q55">
-        <v>-4.031530019199998</v>
+        <v>-4.623630585600004</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.155087220778347</v>
+        <v>0.1574630299257024</v>
       </c>
       <c r="T55">
-        <v>2.523954290493002</v>
+        <v>2.578822862025459</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1335968997309846</v>
+        <v>0.1311228830692997</v>
       </c>
       <c r="W55">
-        <v>0.1739737425340183</v>
+        <v>0.1744705250796846</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5178174408177698</v>
+        <v>0.508228228950774</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1666470773088528</v>
+        <v>0.1880280523867811</v>
       </c>
       <c r="C56">
-        <v>-36.23076206557195</v>
+        <v>-66.77015500149702</v>
       </c>
       <c r="D56">
-        <v>176.715237934428</v>
+        <v>150.149844998503</v>
       </c>
       <c r="E56">
-        <v>190.396</v>
+        <v>194.37</v>
       </c>
       <c r="F56">
-        <v>214.596</v>
+        <v>218.57</v>
       </c>
       <c r="G56">
         <v>1.65</v>
@@ -5879,45 +5879,45 @@
         <v>21.9</v>
       </c>
       <c r="M56">
-        <v>43.0908768</v>
+        <v>51.538806</v>
       </c>
       <c r="N56">
-        <v>-21.19087680000001</v>
+        <v>-29.638806</v>
       </c>
       <c r="O56">
-        <v>-5.467246214400001</v>
+        <v>-7.646811948000001</v>
       </c>
       <c r="P56">
-        <v>-15.7236305856</v>
+        <v>-21.991994052</v>
       </c>
       <c r="Q56">
-        <v>-4.623630585600004</v>
+        <v>-10.891994052</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1574630299257024</v>
+        <v>0.1612354863194476</v>
       </c>
       <c r="T56">
-        <v>2.578822862025459</v>
+        <v>2.665946566268997</v>
       </c>
       <c r="U56">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1311228830692997</v>
+        <v>0.1096300135474617</v>
       </c>
       <c r="W56">
-        <v>0.1744705250796846</v>
+        <v>0.2099492428055085</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.508228228950774</v>
+        <v>0.4249225331296964</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1880280523867811</v>
+        <v>0.1899280523867811</v>
       </c>
       <c r="C57">
-        <v>-66.77015500149702</v>
+        <v>-72.72353861747459</v>
       </c>
       <c r="D57">
-        <v>150.149844998503</v>
+        <v>148.1704613825254</v>
       </c>
       <c r="E57">
-        <v>194.37</v>
+        <v>198.344</v>
       </c>
       <c r="F57">
-        <v>218.57</v>
+        <v>222.544</v>
       </c>
       <c r="G57">
         <v>1.65</v>
@@ -5961,37 +5961,37 @@
         <v>21.9</v>
       </c>
       <c r="M57">
-        <v>51.538806</v>
+        <v>52.4758752</v>
       </c>
       <c r="N57">
-        <v>-29.638806</v>
+        <v>-30.57587520000001</v>
       </c>
       <c r="O57">
-        <v>-7.646811948000001</v>
+        <v>-7.888575801600002</v>
       </c>
       <c r="P57">
-        <v>-21.991994052</v>
+        <v>-22.6872993984</v>
       </c>
       <c r="Q57">
-        <v>-10.891994052</v>
+        <v>-11.5872993984</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1612354863194476</v>
+        <v>0.163859020099435</v>
       </c>
       <c r="T57">
-        <v>2.665946566268997</v>
+        <v>2.726536260956929</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1096300135474617</v>
+        <v>0.1076723347341142</v>
       </c>
       <c r="W57">
-        <v>0.2099492428055085</v>
+        <v>0.2104108634696959</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4249225331296964</v>
+        <v>0.4173346307523804</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1899280523867811</v>
+        <v>0.1918280523867811</v>
       </c>
       <c r="C58">
-        <v>-72.72353861747459</v>
+        <v>-78.625413926536</v>
       </c>
       <c r="D58">
-        <v>148.1704613825254</v>
+        <v>146.242586073464</v>
       </c>
       <c r="E58">
-        <v>198.344</v>
+        <v>202.318</v>
       </c>
       <c r="F58">
-        <v>222.544</v>
+        <v>226.518</v>
       </c>
       <c r="G58">
         <v>1.65</v>
@@ -6043,37 +6043,37 @@
         <v>21.9</v>
       </c>
       <c r="M58">
-        <v>52.4758752</v>
+        <v>53.4129444</v>
       </c>
       <c r="N58">
-        <v>-30.57587520000001</v>
+        <v>-31.5129444</v>
       </c>
       <c r="O58">
-        <v>-7.888575801600002</v>
+        <v>-8.1303396552</v>
       </c>
       <c r="P58">
-        <v>-22.6872993984</v>
+        <v>-23.3826047448</v>
       </c>
       <c r="Q58">
-        <v>-11.5872993984</v>
+        <v>-12.2826047448</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.163859020099435</v>
+        <v>0.1666045787063986</v>
       </c>
       <c r="T58">
-        <v>2.726536260956929</v>
+        <v>2.789944080979184</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1076723347341142</v>
+        <v>0.1057833464054455</v>
       </c>
       <c r="W58">
-        <v>0.2104108634696959</v>
+        <v>0.2108562869175959</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4173346307523804</v>
+        <v>0.4100129705637422</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1918280523867811</v>
+        <v>0.1937280523867811</v>
       </c>
       <c r="C59">
-        <v>-78.625413926536</v>
+        <v>-84.47776565939785</v>
       </c>
       <c r="D59">
-        <v>146.242586073464</v>
+        <v>144.3642343406022</v>
       </c>
       <c r="E59">
-        <v>202.318</v>
+        <v>206.292</v>
       </c>
       <c r="F59">
-        <v>226.518</v>
+        <v>230.492</v>
       </c>
       <c r="G59">
         <v>1.65</v>
@@ -6125,37 +6125,37 @@
         <v>21.9</v>
       </c>
       <c r="M59">
-        <v>53.4129444</v>
+        <v>54.3500136</v>
       </c>
       <c r="N59">
-        <v>-31.5129444</v>
+        <v>-32.45001360000001</v>
       </c>
       <c r="O59">
-        <v>-8.1303396552</v>
+        <v>-8.372103508800002</v>
       </c>
       <c r="P59">
-        <v>-23.3826047448</v>
+        <v>-24.0779100912</v>
       </c>
       <c r="Q59">
-        <v>-12.2826047448</v>
+        <v>-12.9779100912</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1666045787063986</v>
+        <v>0.1694808781994081</v>
       </c>
       <c r="T59">
-        <v>2.789944080979184</v>
+        <v>2.856371321002498</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.1057833464054455</v>
+        <v>0.1039594956053516</v>
       </c>
       <c r="W59">
-        <v>0.2108562869175959</v>
+        <v>0.2112863509362581</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4100129705637422</v>
+        <v>0.4029437814160914</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1937280523867811</v>
+        <v>0.1956280523867811</v>
       </c>
       <c r="C60">
-        <v>-84.47776565939779</v>
+        <v>-90.28247787168138</v>
       </c>
       <c r="D60">
-        <v>144.3642343406022</v>
+        <v>142.5335221283186</v>
       </c>
       <c r="E60">
-        <v>206.292</v>
+        <v>210.266</v>
       </c>
       <c r="F60">
-        <v>230.492</v>
+        <v>234.466</v>
       </c>
       <c r="G60">
         <v>1.65</v>
@@ -6207,37 +6207,37 @@
         <v>21.9</v>
       </c>
       <c r="M60">
-        <v>54.35001359999999</v>
+        <v>55.2870828</v>
       </c>
       <c r="N60">
-        <v>-32.45001359999999</v>
+        <v>-33.3870828</v>
       </c>
       <c r="O60">
-        <v>-8.372103508799999</v>
+        <v>-8.613867362400001</v>
       </c>
       <c r="P60">
-        <v>-24.07791009119999</v>
+        <v>-24.7732154376</v>
       </c>
       <c r="Q60">
-        <v>-12.97791009119999</v>
+        <v>-13.6732154376</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1694808781994081</v>
+        <v>0.1724974849847595</v>
       </c>
       <c r="T60">
-        <v>2.856371321002496</v>
+        <v>2.926038914197679</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.1039594956053516</v>
+        <v>0.1021974702561084</v>
       </c>
       <c r="W60">
-        <v>0.2112863509362581</v>
+        <v>0.2117018365136097</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4029437814160916</v>
+        <v>0.3961142257988696</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1956280523867811</v>
+        <v>0.1975280523867811</v>
       </c>
       <c r="C61">
-        <v>-90.28247787168138</v>
+        <v>-96.04134024738403</v>
       </c>
       <c r="D61">
-        <v>142.5335221283186</v>
+        <v>140.7486597526159</v>
       </c>
       <c r="E61">
-        <v>210.266</v>
+        <v>214.24</v>
       </c>
       <c r="F61">
-        <v>234.466</v>
+        <v>238.44</v>
       </c>
       <c r="G61">
         <v>1.65</v>
@@ -6289,37 +6289,37 @@
         <v>21.9</v>
       </c>
       <c r="M61">
-        <v>55.2870828</v>
+        <v>56.224152</v>
       </c>
       <c r="N61">
-        <v>-33.3870828</v>
+        <v>-34.324152</v>
       </c>
       <c r="O61">
-        <v>-8.613867362400001</v>
+        <v>-8.855631215999999</v>
       </c>
       <c r="P61">
-        <v>-24.7732154376</v>
+        <v>-25.468520784</v>
       </c>
       <c r="Q61">
-        <v>-13.6732154376</v>
+        <v>-14.368520784</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1724974849847595</v>
+        <v>0.1756649221093785</v>
       </c>
       <c r="T61">
-        <v>2.926038914197679</v>
+        <v>2.999189887052621</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1021974702561084</v>
+        <v>0.1004941790851732</v>
       </c>
       <c r="W61">
-        <v>0.2117018365136097</v>
+        <v>0.2121034725717162</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3961142257988696</v>
+        <v>0.3895123220355551</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1975280523867811</v>
+        <v>0.1994280523867811</v>
       </c>
       <c r="C62">
-        <v>-96.04134024738403</v>
+        <v>-101.7560539345998</v>
       </c>
       <c r="D62">
-        <v>140.7486597526159</v>
+        <v>139.0079460654001</v>
       </c>
       <c r="E62">
-        <v>214.24</v>
+        <v>218.214</v>
       </c>
       <c r="F62">
-        <v>238.44</v>
+        <v>242.414</v>
       </c>
       <c r="G62">
         <v>1.65</v>
@@ -6371,37 +6371,37 @@
         <v>21.9</v>
       </c>
       <c r="M62">
-        <v>56.224152</v>
+        <v>57.1612212</v>
       </c>
       <c r="N62">
-        <v>-34.324152</v>
+        <v>-35.2612212</v>
       </c>
       <c r="O62">
-        <v>-8.855631215999999</v>
+        <v>-9.097395069600001</v>
       </c>
       <c r="P62">
-        <v>-25.468520784</v>
+        <v>-26.1638261304</v>
       </c>
       <c r="Q62">
-        <v>-14.368520784</v>
+        <v>-15.0638261304</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1756649221093785</v>
+        <v>0.1789947919070549</v>
       </c>
       <c r="T62">
-        <v>2.999189887052621</v>
+        <v>3.076092191848843</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1004941790851732</v>
+        <v>0.09884673352639987</v>
       </c>
       <c r="W62">
-        <v>0.2121034725717162</v>
+        <v>0.2124919402344749</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3895123220355551</v>
+        <v>0.3831268741333329</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1994280523867811</v>
+        <v>0.2013280523867811</v>
       </c>
       <c r="C63">
-        <v>-101.7560539345998</v>
+        <v>-107.4282369534897</v>
       </c>
       <c r="D63">
-        <v>139.0079460654001</v>
+        <v>137.3097630465103</v>
       </c>
       <c r="E63">
-        <v>218.214</v>
+        <v>222.188</v>
       </c>
       <c r="F63">
-        <v>242.414</v>
+        <v>246.388</v>
       </c>
       <c r="G63">
         <v>1.65</v>
@@ -6453,37 +6453,37 @@
         <v>21.9</v>
       </c>
       <c r="M63">
-        <v>57.1612212</v>
+        <v>58.0982904</v>
       </c>
       <c r="N63">
-        <v>-35.2612212</v>
+        <v>-36.1982904</v>
       </c>
       <c r="O63">
-        <v>-9.097395069600001</v>
+        <v>-9.339158923199999</v>
       </c>
       <c r="P63">
-        <v>-26.1638261304</v>
+        <v>-26.8591314768</v>
       </c>
       <c r="Q63">
-        <v>-15.0638261304</v>
+        <v>-15.7591314768</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1789947919070549</v>
+        <v>0.1824999180098721</v>
       </c>
       <c r="T63">
-        <v>3.076092191848843</v>
+        <v>3.157041986371181</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.09884673352639987</v>
+        <v>0.09725243137274828</v>
       </c>
       <c r="W63">
-        <v>0.2124919402344749</v>
+        <v>0.2128678766823059</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3831268741333329</v>
+        <v>0.376947408421505</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2013280523867811</v>
+        <v>0.2032280523867811</v>
       </c>
       <c r="C64">
-        <v>-107.4282369534897</v>
+        <v>-113.0594292126394</v>
       </c>
       <c r="D64">
-        <v>137.3097630465103</v>
+        <v>135.6525707873606</v>
       </c>
       <c r="E64">
-        <v>222.188</v>
+        <v>226.162</v>
       </c>
       <c r="F64">
-        <v>246.388</v>
+        <v>250.362</v>
       </c>
       <c r="G64">
         <v>1.65</v>
@@ -6535,37 +6535,37 @@
         <v>21.9</v>
       </c>
       <c r="M64">
-        <v>58.0982904</v>
+        <v>59.0353596</v>
       </c>
       <c r="N64">
-        <v>-36.1982904</v>
+        <v>-37.1353596</v>
       </c>
       <c r="O64">
-        <v>-9.339158923199999</v>
+        <v>-9.580922776800001</v>
       </c>
       <c r="P64">
-        <v>-26.8591314768</v>
+        <v>-27.5544368232</v>
       </c>
       <c r="Q64">
-        <v>-15.7591314768</v>
+        <v>-16.4544368232</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1824999180098721</v>
+        <v>0.1861945103885173</v>
       </c>
       <c r="T64">
-        <v>3.157041986371181</v>
+        <v>3.242367445462293</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.09725243137274828</v>
+        <v>0.09570874198587925</v>
       </c>
       <c r="W64">
-        <v>0.2128678766823059</v>
+        <v>0.2132318786397297</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.376947408421505</v>
+        <v>0.3709641162243382</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2032280523867811</v>
+        <v>0.2051280523867811</v>
       </c>
       <c r="C65">
-        <v>-113.0594292126394</v>
+        <v>-118.6510971664928</v>
       </c>
       <c r="D65">
-        <v>135.6525707873606</v>
+        <v>134.0349028335071</v>
       </c>
       <c r="E65">
-        <v>226.162</v>
+        <v>230.136</v>
       </c>
       <c r="F65">
-        <v>250.362</v>
+        <v>254.336</v>
       </c>
       <c r="G65">
         <v>1.65</v>
@@ -6617,37 +6617,37 @@
         <v>21.9</v>
       </c>
       <c r="M65">
-        <v>59.0353596</v>
+        <v>59.9724288</v>
       </c>
       <c r="N65">
-        <v>-37.1353596</v>
+        <v>-38.0724288</v>
       </c>
       <c r="O65">
-        <v>-9.580922776800001</v>
+        <v>-9.8226866304</v>
       </c>
       <c r="P65">
-        <v>-27.5544368232</v>
+        <v>-28.2497421696</v>
       </c>
       <c r="Q65">
-        <v>-16.4544368232</v>
+        <v>-17.1497421696</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1861945103885173</v>
+        <v>0.1900943578993094</v>
       </c>
       <c r="T65">
-        <v>3.242367445462293</v>
+        <v>3.332433207836246</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.09570874198587925</v>
+        <v>0.09421329289234989</v>
       </c>
       <c r="W65">
-        <v>0.2132318786397297</v>
+        <v>0.2135845055359839</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3709641162243382</v>
+        <v>0.3651678019083329</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2051280523867811</v>
+        <v>0.2070280523867811</v>
       </c>
       <c r="C66">
-        <v>-118.6510971664928</v>
+        <v>-124.2046381434733</v>
       </c>
       <c r="D66">
-        <v>134.0349028335071</v>
+        <v>132.4553618565267</v>
       </c>
       <c r="E66">
-        <v>230.136</v>
+        <v>234.11</v>
       </c>
       <c r="F66">
-        <v>254.336</v>
+        <v>258.31</v>
       </c>
       <c r="G66">
         <v>1.65</v>
@@ -6699,37 +6699,37 @@
         <v>21.9</v>
       </c>
       <c r="M66">
-        <v>59.9724288</v>
+        <v>60.90949800000001</v>
       </c>
       <c r="N66">
-        <v>-38.0724288</v>
+        <v>-39.00949800000001</v>
       </c>
       <c r="O66">
-        <v>-9.8226866304</v>
+        <v>-10.064450484</v>
       </c>
       <c r="P66">
-        <v>-28.2497421696</v>
+        <v>-28.94504751600001</v>
       </c>
       <c r="Q66">
-        <v>-17.1497421696</v>
+        <v>-17.84504751600001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1900943578993094</v>
+        <v>0.1942170538392897</v>
       </c>
       <c r="T66">
-        <v>3.332433207836246</v>
+        <v>3.427645585202997</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.09421329289234989</v>
+        <v>0.09276385761708296</v>
       </c>
       <c r="W66">
-        <v>0.2135845055359839</v>
+        <v>0.2139262823738919</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3651678019083329</v>
+        <v>0.3595498357251278</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2070280523867811</v>
+        <v>0.2089280523867811</v>
       </c>
       <c r="C67">
-        <v>-124.2046381434733</v>
+        <v>-129.721384371637</v>
       </c>
       <c r="D67">
-        <v>132.4553618565267</v>
+        <v>130.912615628363</v>
       </c>
       <c r="E67">
-        <v>234.11</v>
+        <v>238.084</v>
       </c>
       <c r="F67">
-        <v>258.31</v>
+        <v>262.284</v>
       </c>
       <c r="G67">
         <v>1.65</v>
@@ -6781,37 +6781,37 @@
         <v>21.9</v>
       </c>
       <c r="M67">
-        <v>60.90949800000001</v>
+        <v>61.8465672</v>
       </c>
       <c r="N67">
-        <v>-39.00949800000001</v>
+        <v>-39.9465672</v>
       </c>
       <c r="O67">
-        <v>-10.064450484</v>
+        <v>-10.3062143376</v>
       </c>
       <c r="P67">
-        <v>-28.94504751600001</v>
+        <v>-29.6403528624</v>
       </c>
       <c r="Q67">
-        <v>-17.84504751600001</v>
+        <v>-18.5403528624</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1942170538392897</v>
+        <v>0.1985822613051512</v>
       </c>
       <c r="T67">
-        <v>3.427645585202997</v>
+        <v>3.528458690650144</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.09276385761708296</v>
+        <v>0.09135834462288474</v>
       </c>
       <c r="W67">
-        <v>0.2139262823738919</v>
+        <v>0.2142577023379238</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3595498357251278</v>
+        <v>0.3541021109414138</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2089280523867811</v>
+        <v>0.2108280523867811</v>
       </c>
       <c r="C68">
-        <v>-129.721384371637</v>
+        <v>-135.2026067262396</v>
       </c>
       <c r="D68">
-        <v>130.912615628363</v>
+        <v>129.4053932737604</v>
       </c>
       <c r="E68">
-        <v>238.084</v>
+        <v>242.058</v>
       </c>
       <c r="F68">
-        <v>262.284</v>
+        <v>266.258</v>
       </c>
       <c r="G68">
         <v>1.65</v>
@@ -6863,37 +6863,37 @@
         <v>21.9</v>
       </c>
       <c r="M68">
-        <v>61.8465672</v>
+        <v>62.7836364</v>
       </c>
       <c r="N68">
-        <v>-39.9465672</v>
+        <v>-40.8836364</v>
       </c>
       <c r="O68">
-        <v>-10.3062143376</v>
+        <v>-10.5479781912</v>
       </c>
       <c r="P68">
-        <v>-29.6403528624</v>
+        <v>-30.3356582088</v>
       </c>
       <c r="Q68">
-        <v>-18.5403528624</v>
+        <v>-19.2356582088</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1985822613051512</v>
+        <v>0.2032120267992467</v>
       </c>
       <c r="T68">
-        <v>3.528458690650144</v>
+        <v>3.635381681275906</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.09135834462288474</v>
+        <v>0.08999478724045364</v>
       </c>
       <c r="W68">
-        <v>0.2142577023379238</v>
+        <v>0.214579229168701</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3541021109414138</v>
+        <v>0.3488170048079597</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2108280523867811</v>
+        <v>0.2127280523867811</v>
       </c>
       <c r="C69">
-        <v>-135.2026067262396</v>
+        <v>-140.6495182213696</v>
       </c>
       <c r="D69">
-        <v>129.4053932737604</v>
+        <v>127.9324817786305</v>
       </c>
       <c r="E69">
-        <v>242.058</v>
+        <v>246.032</v>
       </c>
       <c r="F69">
-        <v>266.258</v>
+        <v>270.232</v>
       </c>
       <c r="G69">
         <v>1.65</v>
@@ -6945,37 +6945,37 @@
         <v>21.9</v>
       </c>
       <c r="M69">
-        <v>62.7836364</v>
+        <v>63.72070560000001</v>
       </c>
       <c r="N69">
-        <v>-40.8836364</v>
+        <v>-41.82070560000001</v>
       </c>
       <c r="O69">
-        <v>-10.5479781912</v>
+        <v>-10.7897420448</v>
       </c>
       <c r="P69">
-        <v>-30.3356582088</v>
+        <v>-31.03096355520001</v>
       </c>
       <c r="Q69">
-        <v>-19.2356582088</v>
+        <v>-19.93096355520001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2032120267992467</v>
+        <v>0.2081311526367231</v>
       </c>
       <c r="T69">
-        <v>3.635381681275906</v>
+        <v>3.748987358815777</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.08999478724045364</v>
+        <v>0.08867133448691752</v>
       </c>
       <c r="W69">
-        <v>0.214579229168701</v>
+        <v>0.2148912993279848</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3488170048079597</v>
+        <v>0.3436873429725485</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2127280523867811</v>
+        <v>0.2146280523867811</v>
       </c>
       <c r="C70">
-        <v>-140.6495182213696</v>
+        <v>-146.0632772658116</v>
       </c>
       <c r="D70">
-        <v>127.9324817786305</v>
+        <v>126.4927227341884</v>
       </c>
       <c r="E70">
-        <v>246.032</v>
+        <v>250.006</v>
       </c>
       <c r="F70">
-        <v>270.232</v>
+        <v>274.206</v>
       </c>
       <c r="G70">
         <v>1.65</v>
@@ -7027,37 +7027,37 @@
         <v>21.9</v>
       </c>
       <c r="M70">
-        <v>63.72070560000001</v>
+        <v>64.65777480000001</v>
       </c>
       <c r="N70">
-        <v>-41.82070560000001</v>
+        <v>-42.75777480000001</v>
       </c>
       <c r="O70">
-        <v>-10.7897420448</v>
+        <v>-11.0315058984</v>
       </c>
       <c r="P70">
-        <v>-31.03096355520001</v>
+        <v>-31.72626890160001</v>
       </c>
       <c r="Q70">
-        <v>-19.93096355520001</v>
+        <v>-20.62626890160001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2081311526367231</v>
+        <v>0.2133676414314561</v>
       </c>
       <c r="T70">
-        <v>3.748987358815777</v>
+        <v>3.869922434906609</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.08867133448691752</v>
+        <v>0.0873862426827593</v>
       </c>
       <c r="W70">
-        <v>0.2148912993279848</v>
+        <v>0.2151943239754054</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3436873429725485</v>
+        <v>0.3387063669874392</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2146280523867811</v>
+        <v>0.2165280523867811</v>
       </c>
       <c r="C71">
-        <v>-146.0632772658116</v>
+        <v>-151.4449907015069</v>
       </c>
       <c r="D71">
-        <v>126.4927227341884</v>
+        <v>125.0850092984931</v>
       </c>
       <c r="E71">
-        <v>250.006</v>
+        <v>253.98</v>
       </c>
       <c r="F71">
-        <v>274.206</v>
+        <v>278.18</v>
       </c>
       <c r="G71">
         <v>1.65</v>
@@ -7109,37 +7109,37 @@
         <v>21.9</v>
       </c>
       <c r="M71">
-        <v>64.65777480000001</v>
+        <v>65.59484400000001</v>
       </c>
       <c r="N71">
-        <v>-42.75777480000001</v>
+        <v>-43.69484400000001</v>
       </c>
       <c r="O71">
-        <v>-11.0315058984</v>
+        <v>-11.273269752</v>
       </c>
       <c r="P71">
-        <v>-31.72626890160001</v>
+        <v>-32.42157424800001</v>
       </c>
       <c r="Q71">
-        <v>-20.62626890160001</v>
+        <v>-21.321574248</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2133676414314561</v>
+        <v>0.2189532294791714</v>
       </c>
       <c r="T71">
-        <v>3.869922434906609</v>
+        <v>3.998919849403496</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0873862426827593</v>
+        <v>0.08613786778729131</v>
       </c>
       <c r="W71">
-        <v>0.2151943239754054</v>
+        <v>0.2154886907757567</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3387063669874392</v>
+        <v>0.3338677046019043</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2165280523867811</v>
+        <v>0.2184280523867811</v>
       </c>
       <c r="C72">
-        <v>-151.4449907015069</v>
+        <v>-156.7957166413595</v>
       </c>
       <c r="D72">
-        <v>125.0850092984931</v>
+        <v>123.7082833586404</v>
       </c>
       <c r="E72">
-        <v>253.98</v>
+        <v>257.954</v>
       </c>
       <c r="F72">
-        <v>278.18</v>
+        <v>282.154</v>
       </c>
       <c r="G72">
         <v>1.65</v>
@@ -7191,37 +7191,37 @@
         <v>21.9</v>
       </c>
       <c r="M72">
-        <v>65.59484400000001</v>
+        <v>66.53191320000001</v>
       </c>
       <c r="N72">
-        <v>-43.69484400000001</v>
+        <v>-44.63191320000001</v>
       </c>
       <c r="O72">
-        <v>-11.273269752</v>
+        <v>-11.5150336056</v>
       </c>
       <c r="P72">
-        <v>-32.42157424800001</v>
+        <v>-33.1168795944</v>
       </c>
       <c r="Q72">
-        <v>-21.321574248</v>
+        <v>-22.0168795944</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2189532294791714</v>
+        <v>0.2249240304956945</v>
       </c>
       <c r="T72">
-        <v>3.998919849403496</v>
+        <v>4.136813637313963</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08613786778729131</v>
+        <v>0.08492465838183652</v>
       </c>
       <c r="W72">
-        <v>0.2154886907757567</v>
+        <v>0.215774765553563</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3338677046019043</v>
+        <v>0.3291653425652578</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2184280523867811</v>
+        <v>0.2203280523867811</v>
       </c>
       <c r="C73">
-        <v>-156.7957166413595</v>
+        <v>-162.1164671216807</v>
       </c>
       <c r="D73">
-        <v>123.7082833586404</v>
+        <v>122.3615328783193</v>
       </c>
       <c r="E73">
-        <v>257.954</v>
+        <v>261.928</v>
       </c>
       <c r="F73">
-        <v>282.154</v>
+        <v>286.128</v>
       </c>
       <c r="G73">
         <v>1.65</v>
@@ -7273,37 +7273,37 @@
         <v>21.9</v>
       </c>
       <c r="M73">
-        <v>66.53191320000001</v>
+        <v>67.4689824</v>
       </c>
       <c r="N73">
-        <v>-44.63191320000001</v>
+        <v>-45.5689824</v>
       </c>
       <c r="O73">
-        <v>-11.5150336056</v>
+        <v>-11.7567974592</v>
       </c>
       <c r="P73">
-        <v>-33.1168795944</v>
+        <v>-33.8121849408</v>
       </c>
       <c r="Q73">
-        <v>-22.0168795944</v>
+        <v>-22.7121849408</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2249240304956945</v>
+        <v>0.2313213172991122</v>
       </c>
       <c r="T73">
-        <v>4.136813637313961</v>
+        <v>4.284556981503745</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08492465838183652</v>
+        <v>0.08374514923764435</v>
       </c>
       <c r="W73">
-        <v>0.215774765553563</v>
+        <v>0.2160528938097635</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3291653425652578</v>
+        <v>0.3245936016962959</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2203280523867811</v>
+        <v>0.2222280523867811</v>
       </c>
       <c r="C74">
-        <v>-162.1164671216807</v>
+        <v>-167.4082105832427</v>
       </c>
       <c r="D74">
-        <v>122.3615328783193</v>
+        <v>121.0437894167572</v>
       </c>
       <c r="E74">
-        <v>261.928</v>
+        <v>265.902</v>
       </c>
       <c r="F74">
-        <v>286.128</v>
+        <v>290.102</v>
       </c>
       <c r="G74">
         <v>1.65</v>
@@ -7355,37 +7355,37 @@
         <v>21.9</v>
       </c>
       <c r="M74">
-        <v>67.4689824</v>
+        <v>68.4060516</v>
       </c>
       <c r="N74">
-        <v>-45.5689824</v>
+        <v>-46.5060516</v>
       </c>
       <c r="O74">
-        <v>-11.7567974592</v>
+        <v>-11.9985613128</v>
       </c>
       <c r="P74">
-        <v>-33.8121849408</v>
+        <v>-34.5074902872</v>
       </c>
       <c r="Q74">
-        <v>-22.7121849408</v>
+        <v>-23.4074902872</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2313213172991122</v>
+        <v>0.2381924771990792</v>
       </c>
       <c r="T74">
-        <v>4.284556981503745</v>
+        <v>4.443244277114995</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08374514923764435</v>
+        <v>0.08259795541247114</v>
       </c>
       <c r="W74">
-        <v>0.2160528938097635</v>
+        <v>0.2163234021137393</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3245936016962959</v>
+        <v>0.3201471140018262</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2222280523867811</v>
+        <v>0.2241280523867811</v>
       </c>
       <c r="C75">
-        <v>-167.4082105832427</v>
+        <v>-172.6718741937274</v>
       </c>
       <c r="D75">
-        <v>121.0437894167572</v>
+        <v>119.7541258062726</v>
       </c>
       <c r="E75">
-        <v>265.902</v>
+        <v>269.876</v>
       </c>
       <c r="F75">
-        <v>290.102</v>
+        <v>294.076</v>
       </c>
       <c r="G75">
         <v>1.65</v>
@@ -7437,37 +7437,37 @@
         <v>21.9</v>
       </c>
       <c r="M75">
-        <v>68.4060516</v>
+        <v>69.34312079999999</v>
       </c>
       <c r="N75">
-        <v>-46.5060516</v>
+        <v>-47.4431208</v>
       </c>
       <c r="O75">
-        <v>-11.9985613128</v>
+        <v>-12.2403251664</v>
       </c>
       <c r="P75">
-        <v>-34.5074902872</v>
+        <v>-35.2027956336</v>
       </c>
       <c r="Q75">
-        <v>-23.4074902872</v>
+        <v>-24.1027956336</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2381924771990792</v>
+        <v>0.2455921878605823</v>
       </c>
       <c r="T75">
-        <v>4.443244277114995</v>
+        <v>4.614138287773264</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08259795541247114</v>
+        <v>0.08148176682581613</v>
       </c>
       <c r="W75">
-        <v>0.2163234021137393</v>
+        <v>0.2165865993824726</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3201471140018262</v>
+        <v>0.3158208016504501</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2241280523867811</v>
+        <v>0.2260280523867811</v>
       </c>
       <c r="C76">
-        <v>-172.6718741937274</v>
+        <v>-177.9083460232716</v>
       </c>
       <c r="D76">
-        <v>119.7541258062726</v>
+        <v>118.4916539767284</v>
       </c>
       <c r="E76">
-        <v>269.876</v>
+        <v>273.85</v>
       </c>
       <c r="F76">
-        <v>294.076</v>
+        <v>298.05</v>
       </c>
       <c r="G76">
         <v>1.65</v>
@@ -7519,37 +7519,37 @@
         <v>21.9</v>
       </c>
       <c r="M76">
-        <v>69.34312079999999</v>
+        <v>70.28018999999999</v>
       </c>
       <c r="N76">
-        <v>-47.4431208</v>
+        <v>-48.38018999999999</v>
       </c>
       <c r="O76">
-        <v>-12.2403251664</v>
+        <v>-12.48208902</v>
       </c>
       <c r="P76">
-        <v>-35.2027956336</v>
+        <v>-35.89810098</v>
       </c>
       <c r="Q76">
-        <v>-24.1027956336</v>
+        <v>-24.79810097999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2455921878605823</v>
+        <v>0.2535838753750056</v>
       </c>
       <c r="T76">
-        <v>4.614138287773264</v>
+        <v>4.798703819284195</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08148176682581613</v>
+        <v>0.08039534326813859</v>
       </c>
       <c r="W76">
-        <v>0.2165865993824726</v>
+        <v>0.2168427780573729</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3158208016504501</v>
+        <v>0.3116098576284441</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2260280523867811</v>
+        <v>0.2279280523867811</v>
       </c>
       <c r="C77">
-        <v>-177.9083460232716</v>
+        <v>-183.1184770838381</v>
       </c>
       <c r="D77">
-        <v>118.4916539767284</v>
+        <v>117.2555229161619</v>
       </c>
       <c r="E77">
-        <v>273.85</v>
+        <v>277.824</v>
       </c>
       <c r="F77">
-        <v>298.05</v>
+        <v>302.024</v>
       </c>
       <c r="G77">
         <v>1.65</v>
@@ -7601,37 +7601,37 @@
         <v>21.9</v>
       </c>
       <c r="M77">
-        <v>70.28018999999999</v>
+        <v>71.2172592</v>
       </c>
       <c r="N77">
-        <v>-48.38018999999999</v>
+        <v>-49.3172592</v>
       </c>
       <c r="O77">
-        <v>-12.48208902</v>
+        <v>-12.7238528736</v>
       </c>
       <c r="P77">
-        <v>-35.89810098</v>
+        <v>-36.5934063264</v>
       </c>
       <c r="Q77">
-        <v>-24.79810097999999</v>
+        <v>-25.4934063264</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2535838753750056</v>
+        <v>0.2622415368489642</v>
       </c>
       <c r="T77">
-        <v>4.798703819284195</v>
+        <v>4.99864981175437</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08039534326813859</v>
+        <v>0.07933750980408411</v>
       </c>
       <c r="W77">
-        <v>0.2168427780573729</v>
+        <v>0.217092215188197</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3116098576284441</v>
+        <v>0.3075097279228066</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2279280523867811</v>
+        <v>0.2298280523867811</v>
       </c>
       <c r="C78">
-        <v>-183.1184770838381</v>
+        <v>-188.303083242254</v>
       </c>
       <c r="D78">
-        <v>117.2555229161619</v>
+        <v>116.044916757746</v>
       </c>
       <c r="E78">
-        <v>277.824</v>
+        <v>281.798</v>
       </c>
       <c r="F78">
-        <v>302.024</v>
+        <v>305.998</v>
       </c>
       <c r="G78">
         <v>1.65</v>
@@ -7683,37 +7683,37 @@
         <v>21.9</v>
       </c>
       <c r="M78">
-        <v>71.2172592</v>
+        <v>72.1543284</v>
       </c>
       <c r="N78">
-        <v>-49.3172592</v>
+        <v>-50.2543284</v>
       </c>
       <c r="O78">
-        <v>-12.7238528736</v>
+        <v>-12.9656167272</v>
       </c>
       <c r="P78">
-        <v>-36.5934063264</v>
+        <v>-37.2887116728</v>
       </c>
       <c r="Q78">
-        <v>-25.4934063264</v>
+        <v>-26.1887116728</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2622415368489642</v>
+        <v>0.2716520384510931</v>
       </c>
       <c r="T78">
-        <v>4.99864981175437</v>
+        <v>5.21598241226543</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07933750980408411</v>
+        <v>0.07830715253390121</v>
       </c>
       <c r="W78">
-        <v>0.217092215188197</v>
+        <v>0.2173351734325061</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3075097279228066</v>
+        <v>0.3035160950926403</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2298280523867811</v>
+        <v>0.2317280523867811</v>
       </c>
       <c r="C79">
-        <v>-188.303083242254</v>
+        <v>-193.462947015952</v>
       </c>
       <c r="D79">
-        <v>116.044916757746</v>
+        <v>114.859052984048</v>
       </c>
       <c r="E79">
-        <v>281.798</v>
+        <v>285.772</v>
       </c>
       <c r="F79">
-        <v>305.998</v>
+        <v>309.972</v>
       </c>
       <c r="G79">
         <v>1.65</v>
@@ -7765,37 +7765,37 @@
         <v>21.9</v>
       </c>
       <c r="M79">
-        <v>72.1543284</v>
+        <v>73.09139759999999</v>
       </c>
       <c r="N79">
-        <v>-50.2543284</v>
+        <v>-51.19139759999999</v>
       </c>
       <c r="O79">
-        <v>-12.9656167272</v>
+        <v>-13.2073805808</v>
       </c>
       <c r="P79">
-        <v>-37.2887116728</v>
+        <v>-37.9840170192</v>
       </c>
       <c r="Q79">
-        <v>-26.1887116728</v>
+        <v>-26.88401701919999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2716520384510931</v>
+        <v>0.28191804019887</v>
       </c>
       <c r="T79">
-        <v>5.21598241226543</v>
+        <v>5.453072521913858</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07830715253390121</v>
+        <v>0.07730321468090248</v>
       </c>
       <c r="W79">
-        <v>0.2173351734325061</v>
+        <v>0.2175719019782432</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3035160950926403</v>
+        <v>0.2996248631042732</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2317280523867811</v>
+        <v>0.2336280523867811</v>
       </c>
       <c r="C80">
-        <v>-193.462947015952</v>
+        <v>-198.5988192597226</v>
       </c>
       <c r="D80">
-        <v>114.859052984048</v>
+        <v>113.6971807402774</v>
       </c>
       <c r="E80">
-        <v>285.772</v>
+        <v>289.746</v>
       </c>
       <c r="F80">
-        <v>309.972</v>
+        <v>313.946</v>
       </c>
       <c r="G80">
         <v>1.65</v>
@@ -7847,37 +7847,37 @@
         <v>21.9</v>
       </c>
       <c r="M80">
-        <v>73.09139759999999</v>
+        <v>74.02846679999999</v>
       </c>
       <c r="N80">
-        <v>-51.19139759999999</v>
+        <v>-52.12846679999999</v>
       </c>
       <c r="O80">
-        <v>-13.2073805808</v>
+        <v>-13.4491444344</v>
       </c>
       <c r="P80">
-        <v>-37.9840170192</v>
+        <v>-38.67932236559999</v>
       </c>
       <c r="Q80">
-        <v>-26.88401701919999</v>
+        <v>-27.57932236559999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.28191804019887</v>
+        <v>0.2931617563988163</v>
       </c>
       <c r="T80">
-        <v>5.453072521913858</v>
+        <v>5.712742642004995</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07730321468090248</v>
+        <v>0.07632469297608094</v>
       </c>
       <c r="W80">
-        <v>0.2175719019782432</v>
+        <v>0.2178026373962401</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2996248631042732</v>
+        <v>0.2958321433181431</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2336280523867811</v>
+        <v>0.2355280523867811</v>
       </c>
       <c r="C81">
-        <v>-198.5988192597226</v>
+        <v>-203.7114207511148</v>
       </c>
       <c r="D81">
-        <v>113.6971807402774</v>
+        <v>112.5585792488852</v>
       </c>
       <c r="E81">
-        <v>289.746</v>
+        <v>293.72</v>
       </c>
       <c r="F81">
-        <v>313.946</v>
+        <v>317.92</v>
       </c>
       <c r="G81">
         <v>1.65</v>
@@ -7929,37 +7929,37 @@
         <v>21.9</v>
       </c>
       <c r="M81">
-        <v>74.02846679999999</v>
+        <v>74.965536</v>
       </c>
       <c r="N81">
-        <v>-52.12846679999999</v>
+        <v>-53.065536</v>
       </c>
       <c r="O81">
-        <v>-13.4491444344</v>
+        <v>-13.690908288</v>
       </c>
       <c r="P81">
-        <v>-38.67932236559999</v>
+        <v>-39.374627712</v>
       </c>
       <c r="Q81">
-        <v>-27.57932236559999</v>
+        <v>-28.274627712</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2931617563988163</v>
+        <v>0.3055298442187571</v>
       </c>
       <c r="T81">
-        <v>5.712742642004995</v>
+        <v>5.998379774105245</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07632469297608094</v>
+        <v>0.07537063431387991</v>
       </c>
       <c r="W81">
-        <v>0.2178026373962401</v>
+        <v>0.2180276044287871</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2958321433181431</v>
+        <v>0.2921342415266663</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2355280523867811</v>
+        <v>0.2374280523867811</v>
       </c>
       <c r="C82">
-        <v>-203.7114207511148</v>
+        <v>-208.8014436815218</v>
       </c>
       <c r="D82">
-        <v>112.5585792488852</v>
+        <v>111.4425563184782</v>
       </c>
       <c r="E82">
-        <v>293.72</v>
+        <v>297.694</v>
       </c>
       <c r="F82">
-        <v>317.92</v>
+        <v>321.894</v>
       </c>
       <c r="G82">
         <v>1.65</v>
@@ -8011,37 +8011,37 @@
         <v>21.9</v>
       </c>
       <c r="M82">
-        <v>74.965536</v>
+        <v>75.90260520000001</v>
       </c>
       <c r="N82">
-        <v>-53.065536</v>
+        <v>-54.00260520000001</v>
       </c>
       <c r="O82">
-        <v>-13.690908288</v>
+        <v>-13.9326721416</v>
       </c>
       <c r="P82">
-        <v>-39.374627712</v>
+        <v>-40.06993305840001</v>
       </c>
       <c r="Q82">
-        <v>-28.274627712</v>
+        <v>-28.96993305840001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3055298442187571</v>
+        <v>0.3191998360197442</v>
       </c>
       <c r="T82">
-        <v>5.998379774105245</v>
+        <v>6.314083972742362</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07537063431387991</v>
+        <v>0.07444013265568385</v>
       </c>
       <c r="W82">
-        <v>0.2180276044287871</v>
+        <v>0.2182470167197898</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2921342415266663</v>
+        <v>0.288527645952263</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2374280523867811</v>
+        <v>0.2393280523867811</v>
       </c>
       <c r="C83">
-        <v>-208.8014436815218</v>
+        <v>-213.8695530594322</v>
       </c>
       <c r="D83">
-        <v>111.4425563184782</v>
+        <v>110.3484469405678</v>
       </c>
       <c r="E83">
-        <v>297.694</v>
+        <v>301.668</v>
       </c>
       <c r="F83">
-        <v>321.894</v>
+        <v>325.868</v>
       </c>
       <c r="G83">
         <v>1.65</v>
@@ -8093,37 +8093,37 @@
         <v>21.9</v>
       </c>
       <c r="M83">
-        <v>75.90260520000001</v>
+        <v>76.83967440000001</v>
       </c>
       <c r="N83">
-        <v>-54.00260520000001</v>
+        <v>-54.93967440000001</v>
       </c>
       <c r="O83">
-        <v>-13.9326721416</v>
+        <v>-14.1744359952</v>
       </c>
       <c r="P83">
-        <v>-40.06993305840001</v>
+        <v>-40.7652384048</v>
       </c>
       <c r="Q83">
-        <v>-28.96993305840001</v>
+        <v>-29.6652384048</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3191998360197442</v>
+        <v>0.334388715798619</v>
       </c>
       <c r="T83">
-        <v>6.314083972742362</v>
+        <v>6.664866415672495</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07444013265568385</v>
+        <v>0.07353232615988284</v>
       </c>
       <c r="W83">
-        <v>0.2182470167197898</v>
+        <v>0.2184610774914997</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.288527645952263</v>
+        <v>0.2850090161235769</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2393280523867811</v>
+        <v>0.2412280523867811</v>
       </c>
       <c r="C84">
-        <v>-213.8695530594322</v>
+        <v>-218.9163880318246</v>
       </c>
       <c r="D84">
-        <v>110.3484469405678</v>
+        <v>109.2756119681754</v>
       </c>
       <c r="E84">
-        <v>301.668</v>
+        <v>305.642</v>
       </c>
       <c r="F84">
-        <v>325.868</v>
+        <v>329.842</v>
       </c>
       <c r="G84">
         <v>1.65</v>
@@ -8175,37 +8175,37 @@
         <v>21.9</v>
       </c>
       <c r="M84">
-        <v>76.83967440000001</v>
+        <v>77.7767436</v>
       </c>
       <c r="N84">
-        <v>-54.93967440000001</v>
+        <v>-55.8767436</v>
       </c>
       <c r="O84">
-        <v>-14.1744359952</v>
+        <v>-14.4161998488</v>
       </c>
       <c r="P84">
-        <v>-40.7652384048</v>
+        <v>-41.46054375120001</v>
       </c>
       <c r="Q84">
-        <v>-29.6652384048</v>
+        <v>-30.36054375120001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.334388715798619</v>
+        <v>0.3513645226103024</v>
       </c>
       <c r="T84">
-        <v>6.664866415672495</v>
+        <v>7.056917381300289</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07353232615988284</v>
+        <v>0.07264639451940232</v>
       </c>
       <c r="W84">
-        <v>0.2184610774914997</v>
+        <v>0.2186699801723249</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2850090161235769</v>
+        <v>0.281575172555823</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2412280523867811</v>
+        <v>0.2431280523867811</v>
       </c>
       <c r="C85">
-        <v>-218.9163880318246</v>
+        <v>-223.9425631292233</v>
       </c>
       <c r="D85">
-        <v>109.2756119681754</v>
+        <v>108.2234368707768</v>
       </c>
       <c r="E85">
-        <v>305.642</v>
+        <v>309.616</v>
       </c>
       <c r="F85">
-        <v>329.842</v>
+        <v>333.816</v>
       </c>
       <c r="G85">
         <v>1.65</v>
@@ -8257,37 +8257,37 @@
         <v>21.9</v>
       </c>
       <c r="M85">
-        <v>77.7767436</v>
+        <v>78.71381280000001</v>
       </c>
       <c r="N85">
-        <v>-55.8767436</v>
+        <v>-56.81381280000002</v>
       </c>
       <c r="O85">
-        <v>-14.4161998488</v>
+        <v>-14.6579637024</v>
       </c>
       <c r="P85">
-        <v>-41.46054375120001</v>
+        <v>-42.15584909760001</v>
       </c>
       <c r="Q85">
-        <v>-30.36054375120001</v>
+        <v>-31.05584909760001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3513645226103024</v>
+        <v>0.3704623052734464</v>
       </c>
       <c r="T85">
-        <v>7.056917381300289</v>
+        <v>7.497974717631558</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07264639451940232</v>
+        <v>0.07178155648940943</v>
       </c>
       <c r="W85">
-        <v>0.2186699801723249</v>
+        <v>0.2188739089797973</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.281575172555823</v>
+        <v>0.2782230871682536</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2431280523867811</v>
+        <v>0.2450280523867811</v>
       </c>
       <c r="C86">
-        <v>-223.9425631292232</v>
+        <v>-228.9486694395096</v>
       </c>
       <c r="D86">
-        <v>108.2234368707768</v>
+        <v>107.1913305604903</v>
       </c>
       <c r="E86">
-        <v>309.616</v>
+        <v>313.59</v>
       </c>
       <c r="F86">
-        <v>333.816</v>
+        <v>337.79</v>
       </c>
       <c r="G86">
         <v>1.65</v>
@@ -8339,37 +8339,37 @@
         <v>21.9</v>
       </c>
       <c r="M86">
-        <v>78.7138128</v>
+        <v>79.650882</v>
       </c>
       <c r="N86">
-        <v>-56.8138128</v>
+        <v>-57.750882</v>
       </c>
       <c r="O86">
-        <v>-14.6579637024</v>
+        <v>-14.899727556</v>
       </c>
       <c r="P86">
-        <v>-42.1558490976</v>
+        <v>-42.851154444</v>
       </c>
       <c r="Q86">
-        <v>-31.0558490976</v>
+        <v>-31.75115444399999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3704623052734462</v>
+        <v>0.3921064589583426</v>
       </c>
       <c r="T86">
-        <v>7.497974717631553</v>
+        <v>7.99783969880699</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07178155648940944</v>
+        <v>0.07093706758953404</v>
       </c>
       <c r="W86">
-        <v>0.2188739089797973</v>
+        <v>0.2190730394623879</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2782230871682536</v>
+        <v>0.2749498743780389</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2450280523867811</v>
+        <v>0.2469280523867811</v>
       </c>
       <c r="C87">
-        <v>-228.9486694395096</v>
+        <v>-233.9352757152034</v>
       </c>
       <c r="D87">
-        <v>107.1913305604903</v>
+        <v>106.1787242847965</v>
       </c>
       <c r="E87">
-        <v>313.59</v>
+        <v>317.564</v>
       </c>
       <c r="F87">
-        <v>337.79</v>
+        <v>341.764</v>
       </c>
       <c r="G87">
         <v>1.65</v>
@@ -8421,37 +8421,37 @@
         <v>21.9</v>
       </c>
       <c r="M87">
-        <v>79.650882</v>
+        <v>80.58795119999999</v>
       </c>
       <c r="N87">
-        <v>-57.750882</v>
+        <v>-58.68795119999999</v>
       </c>
       <c r="O87">
-        <v>-14.899727556</v>
+        <v>-15.1414914096</v>
       </c>
       <c r="P87">
-        <v>-42.851154444</v>
+        <v>-43.54645979039999</v>
       </c>
       <c r="Q87">
-        <v>-31.75115444399999</v>
+        <v>-32.44645979039999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3921064589583426</v>
+        <v>0.4168426345982243</v>
       </c>
       <c r="T87">
-        <v>7.99783969880699</v>
+        <v>8.56911396300749</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07093706758953404</v>
+        <v>0.07011221796639992</v>
       </c>
       <c r="W87">
-        <v>0.2190730394623879</v>
+        <v>0.2192675390035229</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2749498743780389</v>
+        <v>0.2717527828155035</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2469280523867811</v>
+        <v>0.2488280523867811</v>
       </c>
       <c r="C88">
-        <v>-233.9352757152034</v>
+        <v>-238.9029294185685</v>
       </c>
       <c r="D88">
-        <v>106.1787242847965</v>
+        <v>105.1850705814315</v>
       </c>
       <c r="E88">
-        <v>317.564</v>
+        <v>321.538</v>
       </c>
       <c r="F88">
-        <v>341.764</v>
+        <v>345.738</v>
       </c>
       <c r="G88">
         <v>1.65</v>
@@ -8503,37 +8503,37 @@
         <v>21.9</v>
       </c>
       <c r="M88">
-        <v>80.58795119999999</v>
+        <v>81.5250204</v>
       </c>
       <c r="N88">
-        <v>-58.68795119999999</v>
+        <v>-59.6250204</v>
       </c>
       <c r="O88">
-        <v>-15.1414914096</v>
+        <v>-15.3832552632</v>
       </c>
       <c r="P88">
-        <v>-43.54645979039999</v>
+        <v>-44.24176513680001</v>
       </c>
       <c r="Q88">
-        <v>-32.44645979039999</v>
+        <v>-33.1417651368</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4168426345982243</v>
+        <v>0.4453843757211646</v>
       </c>
       <c r="T88">
-        <v>8.56911396300749</v>
+        <v>9.228276575546529</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07011221796639992</v>
+        <v>0.06930633040356773</v>
       </c>
       <c r="W88">
-        <v>0.2192675390035229</v>
+        <v>0.2194575672908387</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2717527828155035</v>
+        <v>0.2686291876107276</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2488280523867811</v>
+        <v>0.2507280523867811</v>
       </c>
       <c r="C89">
-        <v>-238.9029294185685</v>
+        <v>-243.8521577085808</v>
       </c>
       <c r="D89">
-        <v>105.1850705814315</v>
+        <v>104.2098422914192</v>
       </c>
       <c r="E89">
-        <v>321.538</v>
+        <v>325.512</v>
       </c>
       <c r="F89">
-        <v>345.738</v>
+        <v>349.712</v>
       </c>
       <c r="G89">
         <v>1.65</v>
@@ -8585,37 +8585,37 @@
         <v>21.9</v>
       </c>
       <c r="M89">
-        <v>81.5250204</v>
+        <v>82.4620896</v>
       </c>
       <c r="N89">
-        <v>-59.6250204</v>
+        <v>-60.5620896</v>
       </c>
       <c r="O89">
-        <v>-15.3832552632</v>
+        <v>-15.6250191168</v>
       </c>
       <c r="P89">
-        <v>-44.24176513680001</v>
+        <v>-44.9370704832</v>
       </c>
       <c r="Q89">
-        <v>-33.1417651368</v>
+        <v>-33.8370704832</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4453843757211646</v>
+        <v>0.4786830736979283</v>
       </c>
       <c r="T89">
-        <v>9.228276575546529</v>
+        <v>9.99729962350874</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06930633040356773</v>
+        <v>0.06851875846716356</v>
       </c>
       <c r="W89">
-        <v>0.2194575672908387</v>
+        <v>0.2196432767534428</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2686291876107276</v>
+        <v>0.2655765832060603</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2507280523867811</v>
+        <v>0.2526280523867811</v>
       </c>
       <c r="C90">
-        <v>-243.8521577085808</v>
+        <v>-248.7834683734969</v>
       </c>
       <c r="D90">
-        <v>104.2098422914192</v>
+        <v>103.252531626503</v>
       </c>
       <c r="E90">
-        <v>325.512</v>
+        <v>329.486</v>
       </c>
       <c r="F90">
-        <v>349.712</v>
+        <v>353.686</v>
       </c>
       <c r="G90">
         <v>1.65</v>
@@ -8667,37 +8667,37 @@
         <v>21.9</v>
       </c>
       <c r="M90">
-        <v>82.4620896</v>
+        <v>83.3991588</v>
       </c>
       <c r="N90">
-        <v>-60.5620896</v>
+        <v>-61.4991588</v>
       </c>
       <c r="O90">
-        <v>-15.6250191168</v>
+        <v>-15.8667829704</v>
       </c>
       <c r="P90">
-        <v>-44.9370704832</v>
+        <v>-45.63237582959999</v>
       </c>
       <c r="Q90">
-        <v>-33.8370704832</v>
+        <v>-34.53237582959999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4786830736979283</v>
+        <v>0.51803608039774</v>
       </c>
       <c r="T90">
-        <v>9.99729962350874</v>
+        <v>10.90614504382772</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06851875846716356</v>
+        <v>0.06774888477652127</v>
       </c>
       <c r="W90">
-        <v>0.2196432767534428</v>
+        <v>0.2198248129696963</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2655765832060603</v>
+        <v>0.2625925766531833</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2526280523867811</v>
+        <v>0.2545280523867811</v>
       </c>
       <c r="C91">
-        <v>-248.7834683734969</v>
+        <v>-253.6973507124881</v>
       </c>
       <c r="D91">
-        <v>103.252531626503</v>
+        <v>102.3126492875119</v>
       </c>
       <c r="E91">
-        <v>329.486</v>
+        <v>333.46</v>
       </c>
       <c r="F91">
-        <v>353.686</v>
+        <v>357.66</v>
       </c>
       <c r="G91">
         <v>1.65</v>
@@ -8749,37 +8749,37 @@
         <v>21.9</v>
       </c>
       <c r="M91">
-        <v>83.3991588</v>
+        <v>84.33622799999999</v>
       </c>
       <c r="N91">
-        <v>-61.4991588</v>
+        <v>-62.43622799999999</v>
       </c>
       <c r="O91">
-        <v>-15.8667829704</v>
+        <v>-16.108546824</v>
       </c>
       <c r="P91">
-        <v>-45.63237582959999</v>
+        <v>-46.327681176</v>
       </c>
       <c r="Q91">
-        <v>-34.53237582959999</v>
+        <v>-35.227681176</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.51803608039774</v>
+        <v>0.565259688437514</v>
       </c>
       <c r="T91">
-        <v>10.90614504382772</v>
+        <v>11.99675954821049</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06774888477652127</v>
+        <v>0.06699611939011549</v>
       </c>
       <c r="W91">
-        <v>0.2198248129696963</v>
+        <v>0.2200023150478108</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2625925766531833</v>
+        <v>0.2596748813570368</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2545280523867811</v>
+        <v>0.2564280523867811</v>
       </c>
       <c r="C92">
-        <v>-253.6973507124881</v>
+        <v>-258.5942763695573</v>
       </c>
       <c r="D92">
-        <v>102.3126492875119</v>
+        <v>101.3897236304427</v>
       </c>
       <c r="E92">
-        <v>333.46</v>
+        <v>337.434</v>
       </c>
       <c r="F92">
-        <v>357.66</v>
+        <v>361.634</v>
       </c>
       <c r="G92">
         <v>1.65</v>
@@ -8831,37 +8831,37 @@
         <v>21.9</v>
       </c>
       <c r="M92">
-        <v>84.33622799999999</v>
+        <v>85.2732972</v>
       </c>
       <c r="N92">
-        <v>-62.43622799999999</v>
+        <v>-63.3732972</v>
       </c>
       <c r="O92">
-        <v>-16.108546824</v>
+        <v>-16.3503106776</v>
       </c>
       <c r="P92">
-        <v>-46.327681176</v>
+        <v>-47.0229865224</v>
       </c>
       <c r="Q92">
-        <v>-35.227681176</v>
+        <v>-35.9229865224</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.565259688437514</v>
+        <v>0.622977431597238</v>
       </c>
       <c r="T92">
-        <v>11.99675954821049</v>
+        <v>13.32973283134499</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06699611939011549</v>
+        <v>0.0662598982979164</v>
       </c>
       <c r="W92">
-        <v>0.2200023150478108</v>
+        <v>0.2201759159813513</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2596748813570368</v>
+        <v>0.2568213112322342</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2564280523867811</v>
+        <v>0.2583280523867811</v>
       </c>
       <c r="C93">
-        <v>-258.5942763695573</v>
+        <v>-263.4747001227249</v>
       </c>
       <c r="D93">
-        <v>101.3897236304427</v>
+        <v>100.483299877275</v>
       </c>
       <c r="E93">
-        <v>337.434</v>
+        <v>341.408</v>
       </c>
       <c r="F93">
-        <v>361.634</v>
+        <v>365.608</v>
       </c>
       <c r="G93">
         <v>1.65</v>
@@ -8913,37 +8913,37 @@
         <v>21.9</v>
       </c>
       <c r="M93">
-        <v>85.2732972</v>
+        <v>86.2103664</v>
       </c>
       <c r="N93">
-        <v>-63.3732972</v>
+        <v>-64.31036639999999</v>
       </c>
       <c r="O93">
-        <v>-16.3503106776</v>
+        <v>-16.5920745312</v>
       </c>
       <c r="P93">
-        <v>-47.0229865224</v>
+        <v>-47.71829186879999</v>
       </c>
       <c r="Q93">
-        <v>-35.9229865224</v>
+        <v>-36.61829186879999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.622977431597238</v>
+        <v>0.6951246105468928</v>
       </c>
       <c r="T93">
-        <v>13.32973283134499</v>
+        <v>14.99594943526312</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0662598982979164</v>
+        <v>0.06553968201206949</v>
       </c>
       <c r="W93">
-        <v>0.2201759159813513</v>
+        <v>0.220345742981554</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2568213112322342</v>
+        <v>0.2540297752405795</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2583280523867811</v>
+        <v>0.2602280523867811</v>
       </c>
       <c r="C94">
-        <v>-263.4747001227249</v>
+        <v>-268.3390606312579</v>
       </c>
       <c r="D94">
-        <v>100.483299877275</v>
+        <v>99.59293936874207</v>
       </c>
       <c r="E94">
-        <v>341.408</v>
+        <v>345.382</v>
       </c>
       <c r="F94">
-        <v>365.608</v>
+        <v>369.582</v>
       </c>
       <c r="G94">
         <v>1.65</v>
@@ -8995,37 +8995,37 @@
         <v>21.9</v>
       </c>
       <c r="M94">
-        <v>86.2103664</v>
+        <v>87.14743560000001</v>
       </c>
       <c r="N94">
-        <v>-64.31036639999999</v>
+        <v>-65.24743560000002</v>
       </c>
       <c r="O94">
-        <v>-16.5920745312</v>
+        <v>-16.8338383848</v>
       </c>
       <c r="P94">
-        <v>-47.71829186879999</v>
+        <v>-48.41359721520001</v>
       </c>
       <c r="Q94">
-        <v>-36.61829186879999</v>
+        <v>-37.31359721520001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6951246105468928</v>
+        <v>0.787885269196449</v>
       </c>
       <c r="T94">
-        <v>14.99594943526312</v>
+        <v>17.13822792601499</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06553968201206949</v>
+        <v>0.06483495424849885</v>
       </c>
       <c r="W94">
-        <v>0.220345742981554</v>
+        <v>0.220511917788204</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2540297752405795</v>
+        <v>0.2512982722810032</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2602280523867811</v>
+        <v>0.2621280523867811</v>
       </c>
       <c r="C95">
-        <v>-268.3390606312579</v>
+        <v>-273.1877811435209</v>
       </c>
       <c r="D95">
-        <v>99.59293936874207</v>
+        <v>98.71821885647913</v>
       </c>
       <c r="E95">
-        <v>345.382</v>
+        <v>349.356</v>
       </c>
       <c r="F95">
-        <v>369.582</v>
+        <v>373.556</v>
       </c>
       <c r="G95">
         <v>1.65</v>
@@ -9077,37 +9077,37 @@
         <v>21.9</v>
       </c>
       <c r="M95">
-        <v>87.14743560000001</v>
+        <v>88.0845048</v>
       </c>
       <c r="N95">
-        <v>-65.24743560000002</v>
+        <v>-66.18450480000001</v>
       </c>
       <c r="O95">
-        <v>-16.8338383848</v>
+        <v>-17.07560223840001</v>
       </c>
       <c r="P95">
-        <v>-48.41359721520001</v>
+        <v>-49.1089025616</v>
       </c>
       <c r="Q95">
-        <v>-37.31359721520001</v>
+        <v>-38.0089025616</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.787885269196449</v>
+        <v>0.9115661473958574</v>
       </c>
       <c r="T95">
-        <v>17.13822792601499</v>
+        <v>19.9945992470175</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06483495424849885</v>
+        <v>0.06414522069266375</v>
       </c>
       <c r="W95">
-        <v>0.220511917788204</v>
+        <v>0.2206745569606699</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2512982722810032</v>
+        <v>0.2486248864056734</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2621280523867811</v>
+        <v>0.2640280523867811</v>
       </c>
       <c r="C96">
-        <v>-273.1877811435209</v>
+        <v>-278.0212701678507</v>
       </c>
       <c r="D96">
-        <v>98.71821885647913</v>
+        <v>97.85872983214934</v>
       </c>
       <c r="E96">
-        <v>349.356</v>
+        <v>353.33</v>
       </c>
       <c r="F96">
-        <v>373.556</v>
+        <v>377.53</v>
       </c>
       <c r="G96">
         <v>1.65</v>
@@ -9159,37 +9159,37 @@
         <v>21.9</v>
       </c>
       <c r="M96">
-        <v>88.0845048</v>
+        <v>89.02157400000002</v>
       </c>
       <c r="N96">
-        <v>-66.18450480000001</v>
+        <v>-67.12157400000001</v>
       </c>
       <c r="O96">
-        <v>-17.07560223840001</v>
+        <v>-17.317366092</v>
       </c>
       <c r="P96">
-        <v>-49.1089025616</v>
+        <v>-49.80420790800001</v>
       </c>
       <c r="Q96">
-        <v>-38.0089025616</v>
+        <v>-38.70420790800001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9115661473958574</v>
+        <v>1.084719376875029</v>
       </c>
       <c r="T96">
-        <v>19.9945992470175</v>
+        <v>23.99351909642101</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06414522069266375</v>
+        <v>0.06347000784326728</v>
       </c>
       <c r="W96">
-        <v>0.2206745569606699</v>
+        <v>0.2208337721505576</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2486248864056734</v>
+        <v>0.2460077823382454</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2640280523867811</v>
+        <v>0.2659280523867811</v>
       </c>
       <c r="C97">
-        <v>-278.0212701678507</v>
+        <v>-282.8399221086873</v>
       </c>
       <c r="D97">
-        <v>97.85872983214934</v>
+        <v>97.01407789131265</v>
       </c>
       <c r="E97">
-        <v>353.33</v>
+        <v>357.304</v>
       </c>
       <c r="F97">
-        <v>377.53</v>
+        <v>381.504</v>
       </c>
       <c r="G97">
         <v>1.65</v>
@@ -9241,37 +9241,37 @@
         <v>21.9</v>
       </c>
       <c r="M97">
-        <v>89.02157400000002</v>
+        <v>89.95864320000001</v>
       </c>
       <c r="N97">
-        <v>-67.12157400000001</v>
+        <v>-68.05864320000001</v>
       </c>
       <c r="O97">
-        <v>-17.317366092</v>
+        <v>-17.5591299456</v>
       </c>
       <c r="P97">
-        <v>-49.80420790800001</v>
+        <v>-50.4995132544</v>
       </c>
       <c r="Q97">
-        <v>-38.70420790800001</v>
+        <v>-39.3995132544</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.084719376875029</v>
+        <v>1.344449221093788</v>
       </c>
       <c r="T97">
-        <v>23.99351909642101</v>
+        <v>29.99189887052627</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06347000784326728</v>
+        <v>0.06280886192823325</v>
       </c>
       <c r="W97">
-        <v>0.2208337721505576</v>
+        <v>0.2209896703573226</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2460077823382454</v>
+        <v>0.243445201272222</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2659280523867811</v>
+        <v>0.2678280523867811</v>
       </c>
       <c r="C98">
-        <v>-282.8399221086872</v>
+        <v>-287.6441178700426</v>
       </c>
       <c r="D98">
-        <v>97.0140778913127</v>
+        <v>96.1838821299573</v>
       </c>
       <c r="E98">
-        <v>357.304</v>
+        <v>361.278</v>
       </c>
       <c r="F98">
-        <v>381.504</v>
+        <v>385.478</v>
       </c>
       <c r="G98">
         <v>1.65</v>
@@ -9323,37 +9323,37 @@
         <v>21.9</v>
       </c>
       <c r="M98">
-        <v>89.9586432</v>
+        <v>90.89571239999999</v>
       </c>
       <c r="N98">
-        <v>-68.05864320000001</v>
+        <v>-68.9957124</v>
       </c>
       <c r="O98">
-        <v>-17.5591299456</v>
+        <v>-17.8008937992</v>
       </c>
       <c r="P98">
-        <v>-50.4995132544</v>
+        <v>-51.19481860080001</v>
       </c>
       <c r="Q98">
-        <v>-39.3995132544</v>
+        <v>-40.0948186008</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.344449221093784</v>
+        <v>1.777332294791712</v>
       </c>
       <c r="T98">
-        <v>29.99189887052619</v>
+        <v>39.98919849403492</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06280886192823326</v>
+        <v>0.06216134788773601</v>
       </c>
       <c r="W98">
-        <v>0.2209896703573226</v>
+        <v>0.2211423541680719</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2434452012722219</v>
+        <v>0.2409354569292093</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2678280523867811</v>
+        <v>0.2697280523867811</v>
       </c>
       <c r="C99">
-        <v>-287.6441178700426</v>
+        <v>-292.4342254282474</v>
       </c>
       <c r="D99">
-        <v>96.1838821299573</v>
+        <v>95.36777457175256</v>
       </c>
       <c r="E99">
-        <v>361.278</v>
+        <v>365.252</v>
       </c>
       <c r="F99">
-        <v>385.478</v>
+        <v>389.452</v>
       </c>
       <c r="G99">
         <v>1.65</v>
@@ -9405,37 +9405,37 @@
         <v>21.9</v>
       </c>
       <c r="M99">
-        <v>90.89571239999999</v>
+        <v>91.8327816</v>
       </c>
       <c r="N99">
-        <v>-68.9957124</v>
+        <v>-69.9327816</v>
       </c>
       <c r="O99">
-        <v>-17.8008937992</v>
+        <v>-18.0426576528</v>
       </c>
       <c r="P99">
-        <v>-51.19481860080001</v>
+        <v>-51.8901239472</v>
       </c>
       <c r="Q99">
-        <v>-40.0948186008</v>
+        <v>-40.79012394719999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.777332294791712</v>
+        <v>2.643098442187568</v>
       </c>
       <c r="T99">
-        <v>39.98919849403492</v>
+        <v>59.98379774105238</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06216134788773601</v>
+        <v>0.0615270484194938</v>
       </c>
       <c r="W99">
-        <v>0.2211423541680719</v>
+        <v>0.2212919219826834</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2409354569292093</v>
+        <v>0.2384769318585032</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2697280523867811</v>
+        <v>0.2716280523867811</v>
       </c>
       <c r="C100">
-        <v>-292.4342254282474</v>
+        <v>-297.2106003757849</v>
       </c>
       <c r="D100">
-        <v>95.36777457175256</v>
+        <v>94.5653996242151</v>
       </c>
       <c r="E100">
-        <v>365.252</v>
+        <v>369.226</v>
       </c>
       <c r="F100">
-        <v>389.452</v>
+        <v>393.426</v>
       </c>
       <c r="G100">
         <v>1.65</v>
@@ -9487,37 +9487,37 @@
         <v>21.9</v>
       </c>
       <c r="M100">
-        <v>91.8327816</v>
+        <v>92.7698508</v>
       </c>
       <c r="N100">
-        <v>-69.9327816</v>
+        <v>-70.86985079999999</v>
       </c>
       <c r="O100">
-        <v>-18.0426576528</v>
+        <v>-18.2844215064</v>
       </c>
       <c r="P100">
-        <v>-51.8901239472</v>
+        <v>-52.5854292936</v>
       </c>
       <c r="Q100">
-        <v>-40.79012394719999</v>
+        <v>-41.4854292936</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.643098442187568</v>
+        <v>5.240396884375135</v>
       </c>
       <c r="T100">
-        <v>59.98379774105238</v>
+        <v>119.9675954821048</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0615270484194938</v>
+        <v>0.06090556308192316</v>
       </c>
       <c r="W100">
-        <v>0.2212919219826834</v>
+        <v>0.2214384682252825</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2384769318585032</v>
+        <v>0.2360680739609425</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2716280523867811</v>
-      </c>
-      <c r="C101">
-        <v>-297.2106003757849</v>
-      </c>
-      <c r="D101">
-        <v>94.5653996242151</v>
-      </c>
-      <c r="E101">
-        <v>369.226</v>
-      </c>
-      <c r="F101">
-        <v>393.426</v>
-      </c>
-      <c r="G101">
-        <v>1.65</v>
-      </c>
-      <c r="H101">
-        <v>373.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>33</v>
-      </c>
-      <c r="K101">
-        <v>11.1</v>
-      </c>
-      <c r="L101">
-        <v>21.9</v>
-      </c>
-      <c r="M101">
-        <v>92.7698508</v>
-      </c>
-      <c r="N101">
-        <v>-70.86985079999999</v>
-      </c>
-      <c r="O101">
-        <v>-18.2844215064</v>
-      </c>
-      <c r="P101">
-        <v>-52.5854292936</v>
-      </c>
-      <c r="Q101">
-        <v>-41.4854292936</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.240396884375135</v>
-      </c>
-      <c r="T101">
-        <v>119.9675954821048</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06090556308192316</v>
-      </c>
-      <c r="W101">
-        <v>0.2214384682252825</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2360680739609425</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
